--- a/25-신분당-성남시-보고서.xlsx
+++ b/25-신분당-성남시-보고서.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\GSMM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\GSMM\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD43EFE-E82E-40D4-8FA2-E5A206DFA748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0006CA77-BDA3-499B-BBCF-5A20E70BD286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-96" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-96" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="149">
   <si>
     <t>시행년도</t>
   </si>
@@ -287,9 +287,6 @@
     <t>상록지하보도 앞 도로</t>
   </si>
   <si>
-    <t>아레나펠리스 버스정류장 앞 도로</t>
-  </si>
-  <si>
     <t>침하 3.5cm</t>
   </si>
   <si>
@@ -403,6 +400,130 @@
   </si>
   <si>
     <t>지반침하 등의 발생이력</t>
+  </si>
+  <si>
+    <t>삼평동 701-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼평동 689-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼평동 688</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼평동 678</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼평동 679</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼평동 675</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼평동 662</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼평동 663</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼평동 651</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백현동 537-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백현동 529-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백현동 556-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백현동 558-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백현동 560</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백현동 564-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백현동 577-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정자동 99-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백궁삼거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정자동 7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정자동 15-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>궁내사거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정자동 17-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정자동 26-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정자동 156-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정자동 156-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정자동 154-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금곡교사거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정자동 168-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정자동 169-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아데나펠리스 버스정류장 앞 도로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불정교사거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -544,7 +665,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -606,6 +727,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -614,10 +739,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4809,7 +4933,9 @@
         <v>일반</v>
       </c>
       <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
+      <c r="Q6" s="4" t="s">
+        <v>118</v>
+      </c>
       <c r="R6" s="4"/>
       <c r="S6" s="5" t="s">
         <v>28</v>
@@ -4871,7 +4997,9 @@
         <v>일반</v>
       </c>
       <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
+      <c r="Q7" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="R7" s="4"/>
       <c r="S7" s="5" t="s">
         <v>29</v>
@@ -4935,7 +5063,9 @@
       <c r="P8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Q8" s="4"/>
+      <c r="Q8" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="R8" s="4"/>
       <c r="S8" s="5" t="s">
         <v>31</v>
@@ -4997,7 +5127,9 @@
         <v>일반</v>
       </c>
       <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
+      <c r="Q9" s="4" t="s">
+        <v>121</v>
+      </c>
       <c r="R9" s="4"/>
       <c r="S9" s="5" t="s">
         <v>33</v>
@@ -5059,7 +5191,9 @@
         <v>일반</v>
       </c>
       <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
+      <c r="Q10" s="4" t="s">
+        <v>122</v>
+      </c>
       <c r="R10" s="4"/>
       <c r="S10" s="5" t="s">
         <v>34</v>
@@ -5121,7 +5255,9 @@
         <v>일반</v>
       </c>
       <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
+      <c r="Q11" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="R11" s="4"/>
       <c r="S11" s="5" t="s">
         <v>36</v>
@@ -5183,7 +5319,9 @@
         <v>일반</v>
       </c>
       <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
+      <c r="Q12" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="R12" s="4"/>
       <c r="S12" s="5" t="s">
         <v>37</v>
@@ -5245,7 +5383,9 @@
         <v>일반</v>
       </c>
       <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
+      <c r="Q13" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="R13" s="4"/>
       <c r="S13" s="5" t="s">
         <v>38</v>
@@ -5307,7 +5447,9 @@
         <v>일반</v>
       </c>
       <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
+      <c r="Q14" s="4" t="s">
+        <v>126</v>
+      </c>
       <c r="R14" s="4"/>
       <c r="S14" s="5" t="s">
         <v>39</v>
@@ -5369,7 +5511,9 @@
         <v>일반</v>
       </c>
       <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
+      <c r="Q15" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="R15" s="4"/>
       <c r="S15" s="5" t="s">
         <v>40</v>
@@ -5433,7 +5577,9 @@
       <c r="P16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="Q16" s="4"/>
+      <c r="Q16" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="R16" s="4"/>
       <c r="S16" s="5" t="s">
         <v>43</v>
@@ -5495,7 +5641,9 @@
         <v>일반</v>
       </c>
       <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
+      <c r="Q17" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="R17" s="4"/>
       <c r="S17" s="5" t="s">
         <v>43</v>
@@ -5557,7 +5705,9 @@
         <v>일반</v>
       </c>
       <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
+      <c r="Q18" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="R18" s="4"/>
       <c r="S18" s="5" t="s">
         <v>45</v>
@@ -5619,7 +5769,9 @@
         <v>일반</v>
       </c>
       <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
+      <c r="Q19" s="4" t="s">
+        <v>130</v>
+      </c>
       <c r="R19" s="4"/>
       <c r="S19" s="5" t="s">
         <v>46</v>
@@ -5681,7 +5833,9 @@
         <v>일반</v>
       </c>
       <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
+      <c r="Q20" s="27" t="s">
+        <v>131</v>
+      </c>
       <c r="R20" s="4"/>
       <c r="S20" s="5" t="s">
         <v>47</v>
@@ -5743,7 +5897,9 @@
         <v>일반</v>
       </c>
       <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
+      <c r="Q21" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="R21" s="4"/>
       <c r="S21" s="5" t="s">
         <v>48</v>
@@ -5805,7 +5961,9 @@
         <v>일반</v>
       </c>
       <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
+      <c r="Q22" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="R22" s="4"/>
       <c r="S22" s="5" t="s">
         <v>49</v>
@@ -5867,7 +6025,9 @@
         <v>일반</v>
       </c>
       <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
+      <c r="Q23" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="R23" s="4"/>
       <c r="S23" s="5" t="s">
         <v>51</v>
@@ -5931,7 +6091,9 @@
       <c r="P24" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Q24" s="4"/>
+      <c r="Q24" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="R24" s="4"/>
       <c r="S24" s="5" t="s">
         <v>51</v>
@@ -5993,7 +6155,9 @@
         <v>일반</v>
       </c>
       <c r="P25" s="4"/>
-      <c r="Q25" s="4"/>
+      <c r="Q25" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="R25" s="4"/>
       <c r="S25" s="5" t="s">
         <v>54</v>
@@ -6057,7 +6221,9 @@
       <c r="P26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Q26" s="4"/>
+      <c r="Q26" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="R26" s="4"/>
       <c r="S26" s="5" t="s">
         <v>55</v>
@@ -6119,7 +6285,9 @@
         <v>일반</v>
       </c>
       <c r="P27" s="4"/>
-      <c r="Q27" s="4"/>
+      <c r="Q27" s="4" t="s">
+        <v>136</v>
+      </c>
       <c r="R27" s="4"/>
       <c r="S27" s="5" t="s">
         <v>56</v>
@@ -6183,7 +6351,9 @@
       <c r="P28" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="Q28" s="4"/>
+      <c r="Q28" s="4" t="s">
+        <v>136</v>
+      </c>
       <c r="R28" s="4"/>
       <c r="S28" s="5" t="s">
         <v>58</v>
@@ -6247,7 +6417,9 @@
       <c r="P29" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="Q29" s="4"/>
+      <c r="Q29" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="R29" s="4"/>
       <c r="S29" s="5" t="s">
         <v>61</v>
@@ -6309,7 +6481,9 @@
         <v>일반</v>
       </c>
       <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
+      <c r="Q30" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="R30" s="4"/>
       <c r="S30" s="5" t="s">
         <v>62</v>
@@ -6373,7 +6547,9 @@
       <c r="P31" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Q31" s="4"/>
+      <c r="Q31" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="R31" s="4"/>
       <c r="S31" s="5" t="s">
         <v>63</v>
@@ -6437,7 +6613,9 @@
       <c r="P32" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="Q32" s="4"/>
+      <c r="Q32" s="4" t="s">
+        <v>139</v>
+      </c>
       <c r="R32" s="4"/>
       <c r="S32" s="5" t="s">
         <v>64</v>
@@ -6499,7 +6677,9 @@
         <v>일반</v>
       </c>
       <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
+      <c r="Q33" s="4" t="s">
+        <v>139</v>
+      </c>
       <c r="R33" s="4"/>
       <c r="S33" s="5" t="s">
         <v>66</v>
@@ -6563,7 +6743,9 @@
       <c r="P34" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Q34" s="4"/>
+      <c r="Q34" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="R34" s="4"/>
       <c r="S34" s="5" t="s">
         <v>67</v>
@@ -6627,7 +6809,9 @@
       <c r="P35" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="Q35" s="4"/>
+      <c r="Q35" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="R35" s="4"/>
       <c r="S35" s="5" t="s">
         <v>69</v>
@@ -6689,7 +6873,9 @@
         <v>일반</v>
       </c>
       <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
+      <c r="Q36" s="4" t="s">
+        <v>141</v>
+      </c>
       <c r="R36" s="4"/>
       <c r="S36" s="5" t="s">
         <v>70</v>
@@ -6751,7 +6937,9 @@
         <v>일반</v>
       </c>
       <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
+      <c r="Q37" s="4" t="s">
+        <v>141</v>
+      </c>
       <c r="R37" s="4"/>
       <c r="S37" s="5" t="s">
         <v>72</v>
@@ -6813,7 +7001,9 @@
         <v>일반</v>
       </c>
       <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
+      <c r="Q38" s="4" t="s">
+        <v>142</v>
+      </c>
       <c r="R38" s="4"/>
       <c r="S38" s="5" t="s">
         <v>73</v>
@@ -6875,7 +7065,9 @@
         <v>일반</v>
       </c>
       <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
+      <c r="Q39" s="4" t="s">
+        <v>142</v>
+      </c>
       <c r="R39" s="4"/>
       <c r="S39" s="5" t="s">
         <v>74</v>
@@ -6937,7 +7129,9 @@
         <v>일반</v>
       </c>
       <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
+      <c r="Q40" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="R40" s="4"/>
       <c r="S40" s="5" t="s">
         <v>75</v>
@@ -6999,7 +7193,9 @@
         <v>일반</v>
       </c>
       <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
+      <c r="Q41" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="R41" s="4"/>
       <c r="S41" s="5" t="s">
         <v>76</v>
@@ -7061,7 +7257,9 @@
         <v>일반</v>
       </c>
       <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
+      <c r="Q42" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="R42" s="4"/>
       <c r="S42" s="5" t="s">
         <v>77</v>
@@ -7123,7 +7321,9 @@
         <v>일반</v>
       </c>
       <c r="P43" s="4"/>
-      <c r="Q43" s="4"/>
+      <c r="Q43" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="R43" s="4"/>
       <c r="S43" s="5" t="s">
         <v>78</v>
@@ -7185,7 +7385,9 @@
         <v>일반</v>
       </c>
       <c r="P44" s="4"/>
-      <c r="Q44" s="4"/>
+      <c r="Q44" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="R44" s="4"/>
       <c r="S44" s="5" t="s">
         <v>79</v>
@@ -7247,10 +7449,12 @@
         <v>일반</v>
       </c>
       <c r="P45" s="4"/>
-      <c r="Q45" s="4"/>
+      <c r="Q45" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="R45" s="4"/>
       <c r="S45" s="5" t="s">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="T45" s="15"/>
     </row>
@@ -7309,12 +7513,14 @@
         <v>일반</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q46" s="4"/>
+        <v>80</v>
+      </c>
+      <c r="Q46" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="R46" s="4"/>
       <c r="S46" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T46" s="15"/>
     </row>
@@ -7373,10 +7579,12 @@
         <v>일반</v>
       </c>
       <c r="P47" s="4"/>
-      <c r="Q47" s="4"/>
+      <c r="Q47" s="4" t="s">
+        <v>148</v>
+      </c>
       <c r="R47" s="4"/>
       <c r="S47" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T47" s="15"/>
     </row>
@@ -7400,19 +7608,19 @@
     <row r="1" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7852,7 +8060,7 @@
       <c r="B44" s="4"/>
       <c r="C44" s="12" t="str">
         <f>IF(RawData!S45="","-",RawData!S45)</f>
-        <v>아레나펠리스 버스정류장 앞 도로</v>
+        <v>아데나펠리스 버스정류장 앞 도로</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7917,7 +8125,7 @@
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="9"/>
@@ -7954,64 +8162,64 @@
       <c r="P3" s="9"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="21" t="s">
+      <c r="D4" s="25"/>
+      <c r="E4" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="21" t="s">
+      <c r="F4" s="25"/>
+      <c r="G4" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="21" t="s">
+      <c r="H4" s="24"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="H4" s="22"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="21" t="s">
+      <c r="K4" s="24"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="22"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="21" t="s">
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="25"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="23"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="25"/>
+      <c r="E5" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="21" t="s">
+      <c r="F5" s="25"/>
+      <c r="G5" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="21" t="s">
+      <c r="H5" s="24"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="K5" s="24"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="K5" s="22"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="23"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="25"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
@@ -8032,43 +8240,43 @@
       <c r="P6" s="9"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="25" t="s">
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="O7" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="P7" s="25" t="s">
+      <c r="P7" s="21" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
       <c r="D8" s="18" t="s">
         <v>8</v>
       </c>
@@ -8082,7 +8290,7 @@
         <v>11</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I8" s="18" t="s">
         <v>13</v>
@@ -8099,9 +8307,9 @@
       <c r="M8" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
       <c r="Q8"/>
       <c r="R8"/>
       <c r="S8"/>
@@ -10845,14 +11053,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="M4:P4"/>
     <mergeCell ref="I7:M7"/>
     <mergeCell ref="G5:I5"/>
@@ -10865,6 +11065,14 @@
     <mergeCell ref="N7:N8"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="B7:B8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10898,16 +11106,16 @@
         <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -10918,7 +11126,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>13</v>
@@ -10933,10 +11141,10 @@
         <v>9</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>27</v>
@@ -10947,10 +11155,10 @@
         <v>2019</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -10965,13 +11173,13 @@
         <v>3</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -10979,7 +11187,7 @@
         <v>2020</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -10991,19 +11199,19 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H4" s="1">
         <v>9</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="L4" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -11011,7 +11219,7 @@
         <v>2021</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>14</v>
@@ -11031,10 +11239,10 @@
         <v>2022</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>

--- a/25-신분당-성남시-보고서.xlsx
+++ b/25-신분당-성남시-보고서.xlsx
@@ -3339,7 +3339,7 @@
         <v>삼환하이펙스 B동 코이라멘_판교점 앞 횡단보도(판교역로230)</v>
       </c>
       <c r="T50" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -3401,7 +3401,7 @@
         <v>솔리드카페 앞 도로(판교역로220)</v>
       </c>
       <c r="T51" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -3463,7 +3463,7 @@
         <v>판교타워 앞 도로(판교역로192번길16</v>
       </c>
       <c r="T52" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/25-신분당-성남시-보고서.xlsx
+++ b/25-신분당-성남시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T52"/>
+  <dimension ref="A1:T60"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3466,9 +3466,505 @@
         <v/>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>26-07</v>
+      </c>
+      <c r="B53" t="str">
+        <v>판교역로</v>
+      </c>
+      <c r="C53" t="str">
+        <v>26-성남시-07</v>
+      </c>
+      <c r="D53" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E53" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F53" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G53" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H53" t="str">
+        <v>-</v>
+      </c>
+      <c r="I53" t="str">
+        <v>0</v>
+      </c>
+      <c r="J53" t="str">
+        <v>3</v>
+      </c>
+      <c r="K53" t="str">
+        <v>0</v>
+      </c>
+      <c r="L53" t="str">
+        <v>1</v>
+      </c>
+      <c r="M53" t="str">
+        <v>0</v>
+      </c>
+      <c r="N53" t="str">
+        <v>4</v>
+      </c>
+      <c r="O53" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P53" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q53" t="str">
+        <v>백현동539</v>
+      </c>
+      <c r="R53" t="str">
+        <v/>
+      </c>
+      <c r="S53" t="str">
+        <v>판교공영주차장 앞 횡단보도(판교역로146번길8)</v>
+      </c>
+      <c r="T53" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>26-08</v>
+      </c>
+      <c r="B54" t="str">
+        <v>서현로</v>
+      </c>
+      <c r="C54" t="str">
+        <v>26-성남시-08</v>
+      </c>
+      <c r="D54" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E54" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F54" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G54" t="str">
+        <v>14-5</v>
+      </c>
+      <c r="H54" t="str">
+        <v>-</v>
+      </c>
+      <c r="I54" t="str">
+        <v>0</v>
+      </c>
+      <c r="J54" t="str">
+        <v>3</v>
+      </c>
+      <c r="K54" t="str">
+        <v>0</v>
+      </c>
+      <c r="L54" t="str">
+        <v>1</v>
+      </c>
+      <c r="M54" t="str">
+        <v>0</v>
+      </c>
+      <c r="N54" t="str">
+        <v>4</v>
+      </c>
+      <c r="O54" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P54" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q54" t="str">
+        <v>백현동554-3</v>
+      </c>
+      <c r="R54" t="str">
+        <v/>
+      </c>
+      <c r="S54" t="str">
+        <v>낙생육교 버스정류장 앞 도로</v>
+      </c>
+      <c r="T54" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>26-09</v>
+      </c>
+      <c r="B55" t="str">
+        <v>동판교로</v>
+      </c>
+      <c r="C55" t="str">
+        <v>26-성남시-09</v>
+      </c>
+      <c r="D55" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E55" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F55" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G55" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H55" t="str">
+        <v>-</v>
+      </c>
+      <c r="I55" t="str">
+        <v>0</v>
+      </c>
+      <c r="J55" t="str">
+        <v>3</v>
+      </c>
+      <c r="K55" t="str">
+        <v>0</v>
+      </c>
+      <c r="L55" t="str">
+        <v>1</v>
+      </c>
+      <c r="M55" t="str">
+        <v>0</v>
+      </c>
+      <c r="N55" t="str">
+        <v>4</v>
+      </c>
+      <c r="O55" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P55" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q55" t="str">
+        <v>백현동556-3</v>
+      </c>
+      <c r="R55" t="str">
+        <v/>
+      </c>
+      <c r="S55" t="str">
+        <v>잿넘어육교 밑 도로</v>
+      </c>
+      <c r="T55" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>26-10</v>
+      </c>
+      <c r="B56" t="str">
+        <v>판교역로</v>
+      </c>
+      <c r="C56" t="str">
+        <v>26-성남시-10</v>
+      </c>
+      <c r="D56" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E56" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F56" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G56" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H56" t="str">
+        <v>-</v>
+      </c>
+      <c r="I56" t="str">
+        <v>0</v>
+      </c>
+      <c r="J56" t="str">
+        <v>3</v>
+      </c>
+      <c r="K56" t="str">
+        <v>0</v>
+      </c>
+      <c r="L56" t="str">
+        <v>1</v>
+      </c>
+      <c r="M56" t="str">
+        <v>0</v>
+      </c>
+      <c r="N56" t="str">
+        <v>4</v>
+      </c>
+      <c r="O56" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P56" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q56" t="str">
+        <v>백현동559</v>
+      </c>
+      <c r="R56" t="str">
+        <v/>
+      </c>
+      <c r="S56" t="str">
+        <v>신백현초등학교 병설유치원 앞 도로(판교역로14번길42)</v>
+      </c>
+      <c r="T56" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>26-11</v>
+      </c>
+      <c r="B57" t="str">
+        <v>판교역로</v>
+      </c>
+      <c r="C57" t="str">
+        <v>26-성남시-11</v>
+      </c>
+      <c r="D57" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E57" t="str">
+        <v>횡균열</v>
+      </c>
+      <c r="F57" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G57" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H57" t="str">
+        <v>-</v>
+      </c>
+      <c r="I57" t="str">
+        <v>0</v>
+      </c>
+      <c r="J57" t="str">
+        <v>1</v>
+      </c>
+      <c r="K57" t="str">
+        <v>0</v>
+      </c>
+      <c r="L57" t="str">
+        <v>1</v>
+      </c>
+      <c r="M57" t="str">
+        <v>0</v>
+      </c>
+      <c r="N57" t="str">
+        <v>2</v>
+      </c>
+      <c r="O57" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P57" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q57" t="str">
+        <v>백현동558</v>
+      </c>
+      <c r="R57" t="str">
+        <v/>
+      </c>
+      <c r="S57" t="str">
+        <v>백현마을8단지 아파트 입구</v>
+      </c>
+      <c r="T57" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>26-12</v>
+      </c>
+      <c r="B58" t="str">
+        <v>판교역로</v>
+      </c>
+      <c r="C58" t="str">
+        <v>26-성남시-12</v>
+      </c>
+      <c r="D58" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E58" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F58" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G58" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H58" t="str">
+        <v>-</v>
+      </c>
+      <c r="I58" t="str">
+        <v>0</v>
+      </c>
+      <c r="J58" t="str">
+        <v>3</v>
+      </c>
+      <c r="K58" t="str">
+        <v>0</v>
+      </c>
+      <c r="L58" t="str">
+        <v>1</v>
+      </c>
+      <c r="M58" t="str">
+        <v>0</v>
+      </c>
+      <c r="N58" t="str">
+        <v>4</v>
+      </c>
+      <c r="O58" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P58" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q58" t="str">
+        <v>백현동560</v>
+      </c>
+      <c r="R58" t="str">
+        <v/>
+      </c>
+      <c r="S58" t="str">
+        <v>블레도르 앞 도로(판교역로2번길40)</v>
+      </c>
+      <c r="T58" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>26-13</v>
+      </c>
+      <c r="B59" t="str">
+        <v>판교역로</v>
+      </c>
+      <c r="C59" t="str">
+        <v>26-성남시-13</v>
+      </c>
+      <c r="D59" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E59" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F59" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G59" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H59" t="str">
+        <v>-</v>
+      </c>
+      <c r="I59" t="str">
+        <v>0</v>
+      </c>
+      <c r="J59" t="str">
+        <v>3</v>
+      </c>
+      <c r="K59" t="str">
+        <v>0</v>
+      </c>
+      <c r="L59" t="str">
+        <v>1</v>
+      </c>
+      <c r="M59" t="str">
+        <v>0</v>
+      </c>
+      <c r="N59" t="str">
+        <v>4</v>
+      </c>
+      <c r="O59" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P59" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q59" t="str">
+        <v>백현동564-5</v>
+      </c>
+      <c r="R59" t="str">
+        <v/>
+      </c>
+      <c r="S59" t="str">
+        <v>세븐일레븐 앞 도로(판교역로14번길 20)</v>
+      </c>
+      <c r="T59" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>26-14</v>
+      </c>
+      <c r="B60" t="str">
+        <v>판교역로</v>
+      </c>
+      <c r="C60" t="str">
+        <v>26-성남시-14</v>
+      </c>
+      <c r="D60" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E60" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F60" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G60" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H60" t="str">
+        <v>-</v>
+      </c>
+      <c r="I60" t="str">
+        <v>0</v>
+      </c>
+      <c r="J60" t="str">
+        <v>3</v>
+      </c>
+      <c r="K60" t="str">
+        <v>0</v>
+      </c>
+      <c r="L60" t="str">
+        <v>1</v>
+      </c>
+      <c r="M60" t="str">
+        <v>0</v>
+      </c>
+      <c r="N60" t="str">
+        <v>4</v>
+      </c>
+      <c r="O60" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P60" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q60" t="str">
+        <v>백현동578-10</v>
+      </c>
+      <c r="R60" t="str">
+        <v/>
+      </c>
+      <c r="S60" t="str">
+        <v>앞 도로(판교역로12)</v>
+      </c>
+      <c r="T60" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T60"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-신분당-성남시-보고서.xlsx
+++ b/25-신분당-성남시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T60"/>
+  <dimension ref="A1:T64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3525,7 +3525,7 @@
         <v>판교공영주차장 앞 횡단보도(판교역로146번길8)</v>
       </c>
       <c r="T53" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -3587,7 +3587,7 @@
         <v>낙생육교 버스정류장 앞 도로</v>
       </c>
       <c r="T54" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -3649,7 +3649,7 @@
         <v>잿넘어육교 밑 도로</v>
       </c>
       <c r="T55" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -3711,7 +3711,7 @@
         <v>신백현초등학교 병설유치원 앞 도로(판교역로14번길42)</v>
       </c>
       <c r="T56" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -3773,7 +3773,7 @@
         <v>백현마을8단지 아파트 입구</v>
       </c>
       <c r="T57" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -3835,7 +3835,7 @@
         <v>블레도르 앞 도로(판교역로2번길40)</v>
       </c>
       <c r="T58" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="59">
@@ -3897,7 +3897,7 @@
         <v>세븐일레븐 앞 도로(판교역로14번길 20)</v>
       </c>
       <c r="T59" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -3959,12 +3959,260 @@
         <v>앞 도로(판교역로12)</v>
       </c>
       <c r="T60" t="str">
-        <v>현장확인필요</v>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>26-15</v>
+      </c>
+      <c r="B61" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C61" t="str">
+        <v>26-성남시-15</v>
+      </c>
+      <c r="D61" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E61" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F61" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G61" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H61" t="str">
+        <v>-</v>
+      </c>
+      <c r="I61" t="str">
+        <v>0</v>
+      </c>
+      <c r="J61" t="str">
+        <v>3</v>
+      </c>
+      <c r="K61" t="str">
+        <v>0</v>
+      </c>
+      <c r="L61" t="str">
+        <v>1</v>
+      </c>
+      <c r="M61" t="str">
+        <v>0</v>
+      </c>
+      <c r="N61" t="str">
+        <v>4</v>
+      </c>
+      <c r="O61" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P61" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q61" t="str">
+        <v>정자동7</v>
+      </c>
+      <c r="R61" t="str">
+        <v/>
+      </c>
+      <c r="S61" t="str">
+        <v>두산위브파빌리온 앞 도로(성남대로393)</v>
+      </c>
+      <c r="T61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>26-16</v>
+      </c>
+      <c r="B62" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C62" t="str">
+        <v>26-성남시-16</v>
+      </c>
+      <c r="D62" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E62" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F62" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G62" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H62" t="str">
+        <v>-</v>
+      </c>
+      <c r="I62" t="str">
+        <v>0</v>
+      </c>
+      <c r="J62" t="str">
+        <v>3</v>
+      </c>
+      <c r="K62" t="str">
+        <v>0</v>
+      </c>
+      <c r="L62" t="str">
+        <v>1</v>
+      </c>
+      <c r="M62" t="str">
+        <v>0</v>
+      </c>
+      <c r="N62" t="str">
+        <v>4</v>
+      </c>
+      <c r="O62" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P62" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q62" t="str">
+        <v>정자동15-1</v>
+      </c>
+      <c r="R62" t="str">
+        <v/>
+      </c>
+      <c r="S62" t="str">
+        <v>할머니부뚜막_정자점(성남대로389)</v>
+      </c>
+      <c r="T62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>26-17</v>
+      </c>
+      <c r="B63" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C63" t="str">
+        <v>26-성남시-17</v>
+      </c>
+      <c r="D63" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E63" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F63" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G63" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H63" t="str">
+        <v>-</v>
+      </c>
+      <c r="I63" t="str">
+        <v>0</v>
+      </c>
+      <c r="J63" t="str">
+        <v>3</v>
+      </c>
+      <c r="K63" t="str">
+        <v>0</v>
+      </c>
+      <c r="L63" t="str">
+        <v>1</v>
+      </c>
+      <c r="M63" t="str">
+        <v>0</v>
+      </c>
+      <c r="N63" t="str">
+        <v>4</v>
+      </c>
+      <c r="O63" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P63" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q63" t="str">
+        <v>정자동15-3</v>
+      </c>
+      <c r="R63" t="str">
+        <v/>
+      </c>
+      <c r="S63" t="str">
+        <v>폴라리스빌딩 앞 도로(성남대로381)</v>
+      </c>
+      <c r="T63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>26-18</v>
+      </c>
+      <c r="B64" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C64" t="str">
+        <v>26-성남시-18</v>
+      </c>
+      <c r="D64" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E64" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F64" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G64" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H64" t="str">
+        <v>-</v>
+      </c>
+      <c r="I64" t="str">
+        <v>0</v>
+      </c>
+      <c r="J64" t="str">
+        <v>3</v>
+      </c>
+      <c r="K64" t="str">
+        <v>0</v>
+      </c>
+      <c r="L64" t="str">
+        <v>1</v>
+      </c>
+      <c r="M64" t="str">
+        <v>0</v>
+      </c>
+      <c r="N64" t="str">
+        <v>4</v>
+      </c>
+      <c r="O64" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P64" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q64" t="str">
+        <v>정자동15-4</v>
+      </c>
+      <c r="R64" t="str">
+        <v/>
+      </c>
+      <c r="S64" t="str">
+        <v>위브제니스아파트 앞 도로(정자일로232번길25)</v>
+      </c>
+      <c r="T64" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T64"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-신분당-성남시-보고서.xlsx
+++ b/25-신분당-성남시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T64"/>
+  <dimension ref="A1:T71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4210,9 +4210,443 @@
         <v/>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>26-19</v>
+      </c>
+      <c r="B65" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C65" t="str">
+        <v>26-성남시-19</v>
+      </c>
+      <c r="D65" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E65" t="str">
+        <v>종균열</v>
+      </c>
+      <c r="F65" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G65" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H65" t="str">
+        <v>-</v>
+      </c>
+      <c r="I65" t="str">
+        <v>0</v>
+      </c>
+      <c r="J65" t="str">
+        <v>1</v>
+      </c>
+      <c r="K65" t="str">
+        <v>0</v>
+      </c>
+      <c r="L65" t="str">
+        <v>1</v>
+      </c>
+      <c r="M65" t="str">
+        <v>0</v>
+      </c>
+      <c r="N65" t="str">
+        <v>2</v>
+      </c>
+      <c r="O65" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P65" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q65" t="str">
+        <v>정자동17-2</v>
+      </c>
+      <c r="R65" t="str">
+        <v/>
+      </c>
+      <c r="S65" t="str">
+        <v>정자역 #5번출구 앞 도로(느티로22)</v>
+      </c>
+      <c r="T65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>26-20</v>
+      </c>
+      <c r="B66" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C66" t="str">
+        <v>26-성남시-20</v>
+      </c>
+      <c r="D66" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E66" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F66" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G66" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H66" t="str">
+        <v>-</v>
+      </c>
+      <c r="I66" t="str">
+        <v>0</v>
+      </c>
+      <c r="J66" t="str">
+        <v>3</v>
+      </c>
+      <c r="K66" t="str">
+        <v>0</v>
+      </c>
+      <c r="L66" t="str">
+        <v>1</v>
+      </c>
+      <c r="M66" t="str">
+        <v>0</v>
+      </c>
+      <c r="N66" t="str">
+        <v>4</v>
+      </c>
+      <c r="O66" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P66" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q66" t="str">
+        <v>정자동17-6</v>
+      </c>
+      <c r="R66" t="str">
+        <v/>
+      </c>
+      <c r="S66" t="str">
+        <v>기아_분당지점 앞 도로(성남대로345)</v>
+      </c>
+      <c r="T66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>26-21</v>
+      </c>
+      <c r="B67" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C67" t="str">
+        <v>26-성남시-21</v>
+      </c>
+      <c r="D67" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E67" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F67" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G67" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H67" t="str">
+        <v>-</v>
+      </c>
+      <c r="I67" t="str">
+        <v>0</v>
+      </c>
+      <c r="J67" t="str">
+        <v>0</v>
+      </c>
+      <c r="K67" t="str">
+        <v>0</v>
+      </c>
+      <c r="L67" t="str">
+        <v>1</v>
+      </c>
+      <c r="M67" t="str">
+        <v>0</v>
+      </c>
+      <c r="N67" t="str">
+        <v>1</v>
+      </c>
+      <c r="O67" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P67" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q67" t="str">
+        <v>정자동99-5</v>
+      </c>
+      <c r="R67" t="str">
+        <v/>
+      </c>
+      <c r="S67" t="str">
+        <v>정자역 프라자빌딩 맞음편 버스정류장 앞 도로(성남대로345)</v>
+      </c>
+      <c r="T67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>26-22</v>
+      </c>
+      <c r="B68" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C68" t="str">
+        <v>26-성남시-22</v>
+      </c>
+      <c r="D68" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E68" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F68" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G68" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H68" t="str">
+        <v>-</v>
+      </c>
+      <c r="I68" t="str">
+        <v>0</v>
+      </c>
+      <c r="J68" t="str">
+        <v>3</v>
+      </c>
+      <c r="K68" t="str">
+        <v>0</v>
+      </c>
+      <c r="L68" t="str">
+        <v>1</v>
+      </c>
+      <c r="M68" t="str">
+        <v>0</v>
+      </c>
+      <c r="N68" t="str">
+        <v>4</v>
+      </c>
+      <c r="O68" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P68" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q68" t="str">
+        <v>정자동26-1</v>
+      </c>
+      <c r="R68" t="str">
+        <v/>
+      </c>
+      <c r="S68" t="str">
+        <v>정자역 #3번출구 앞 양차선</v>
+      </c>
+      <c r="T68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>26-23</v>
+      </c>
+      <c r="B69" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C69" t="str">
+        <v>26-성남시-23</v>
+      </c>
+      <c r="D69" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E69" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F69" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G69" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H69" t="str">
+        <v>-</v>
+      </c>
+      <c r="I69" t="str">
+        <v>0</v>
+      </c>
+      <c r="J69" t="str">
+        <v>3</v>
+      </c>
+      <c r="K69" t="str">
+        <v>0</v>
+      </c>
+      <c r="L69" t="str">
+        <v>1</v>
+      </c>
+      <c r="M69" t="str">
+        <v>0</v>
+      </c>
+      <c r="N69" t="str">
+        <v>4</v>
+      </c>
+      <c r="O69" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P69" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q69" t="str">
+        <v>정자동156-2</v>
+      </c>
+      <c r="R69" t="str">
+        <v/>
+      </c>
+      <c r="S69" t="str">
+        <v>백궁프라자3 앞 양차선(성남대로331번길3-9)</v>
+      </c>
+      <c r="T69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>26-24</v>
+      </c>
+      <c r="B70" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C70" t="str">
+        <v>26-성남시-24</v>
+      </c>
+      <c r="D70" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E70" t="str">
+        <v>종,횡균열</v>
+      </c>
+      <c r="F70" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G70" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H70" t="str">
+        <v>-</v>
+      </c>
+      <c r="I70" t="str">
+        <v>0</v>
+      </c>
+      <c r="J70" t="str">
+        <v>1</v>
+      </c>
+      <c r="K70" t="str">
+        <v>0</v>
+      </c>
+      <c r="L70" t="str">
+        <v>1</v>
+      </c>
+      <c r="M70" t="str">
+        <v>0</v>
+      </c>
+      <c r="N70" t="str">
+        <v>2</v>
+      </c>
+      <c r="O70" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P70" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q70" t="str">
+        <v>정자동156-3</v>
+      </c>
+      <c r="R70" t="str">
+        <v/>
+      </c>
+      <c r="S70" t="str">
+        <v>대명제스트빌딩 앞 양차선(성남대로331번길 3-13)</v>
+      </c>
+      <c r="T70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>26-25</v>
+      </c>
+      <c r="B71" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C71" t="str">
+        <v>26-성남시-25</v>
+      </c>
+      <c r="D71" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E71" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F71" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G71" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H71" t="str">
+        <v>-</v>
+      </c>
+      <c r="I71" t="str">
+        <v>0</v>
+      </c>
+      <c r="J71" t="str">
+        <v>3</v>
+      </c>
+      <c r="K71" t="str">
+        <v>0</v>
+      </c>
+      <c r="L71" t="str">
+        <v>1</v>
+      </c>
+      <c r="M71" t="str">
+        <v>0</v>
+      </c>
+      <c r="N71" t="str">
+        <v>4</v>
+      </c>
+      <c r="O71" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P71" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q71" t="str">
+        <v>금곡교사거리</v>
+      </c>
+      <c r="R71" t="str">
+        <v/>
+      </c>
+      <c r="S71" t="str">
+        <v>금곡교 사거리</v>
+      </c>
+      <c r="T71" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T71"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-신분당-성남시-보고서.xlsx
+++ b/25-신분당-성남시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T71"/>
+  <dimension ref="A1:T75"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,13 +485,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="str">
         <v>판교로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-성남시-1</v>
+        <v>25-성남시-2</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
@@ -533,13 +533,13 @@
         <v/>
       </c>
       <c r="Q5" t="str">
-        <v>삼평동 701-1</v>
+        <v>삼평동 689-1</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>한화에어로 스페이스 앞 횡단보도</v>
+        <v>궁골육교 앞 도로</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -547,13 +547,13 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="str">
         <v>판교로</v>
       </c>
       <c r="C6" t="str">
-        <v>25-성남시-2</v>
+        <v>25-성남시-3</v>
       </c>
       <c r="D6" t="str">
         <v>양호</v>
@@ -592,16 +592,16 @@
         <v>일반</v>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q6" t="str">
-        <v>삼평동 689-1</v>
+        <v>삼평동 688</v>
       </c>
       <c r="R6" t="str">
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>궁골육교 앞 도로</v>
+        <v>한국무역정보통신 버스정류장 앞 도로</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -609,13 +609,13 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" t="str">
-        <v>판교로</v>
+        <v>판교역로</v>
       </c>
       <c r="C7" t="str">
-        <v>25-성남시-3</v>
+        <v>25-성남시-4</v>
       </c>
       <c r="D7" t="str">
         <v>양호</v>
@@ -654,16 +654,16 @@
         <v>일반</v>
       </c>
       <c r="P7" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q7" t="str">
-        <v>삼평동 688</v>
+        <v>삼평동 678</v>
       </c>
       <c r="R7" t="str">
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>한국무역정보통신 버스정류장 앞 도로</v>
+        <v>삼환하이펙스A동 주차장 입출구 앞 횡단보도</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -671,13 +671,13 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="str">
         <v>판교역로</v>
       </c>
       <c r="C8" t="str">
-        <v>25-성남시-4</v>
+        <v>25-성남시-5</v>
       </c>
       <c r="D8" t="str">
         <v>양호</v>
@@ -719,13 +719,13 @@
         <v/>
       </c>
       <c r="Q8" t="str">
-        <v>삼평동 678</v>
+        <v>삼평동 679</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>삼환하이펙스A동 주차장 입출구 앞 횡단보도</v>
+        <v>삼환하이펙스B동 주차장 입출구 앞 횡단보도</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -733,13 +733,13 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="str">
-        <v>판교역로</v>
+        <v>대왕판교로</v>
       </c>
       <c r="C9" t="str">
-        <v>25-성남시-5</v>
+        <v>25-성남시-6</v>
       </c>
       <c r="D9" t="str">
         <v>양호</v>
@@ -781,13 +781,13 @@
         <v/>
       </c>
       <c r="Q9" t="str">
-        <v>삼평동 679</v>
+        <v>삼평동 675</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>삼환하이펙스B동 주차장 입출구 앞 횡단보도</v>
+        <v>SK엔크린 주유소 앞 횡단보도</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -795,13 +795,13 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" t="str">
-        <v>대왕판교로</v>
+        <v>판교역로</v>
       </c>
       <c r="C10" t="str">
-        <v>25-성남시-6</v>
+        <v>25-성남시-7</v>
       </c>
       <c r="D10" t="str">
         <v>양호</v>
@@ -843,13 +843,13 @@
         <v/>
       </c>
       <c r="Q10" t="str">
-        <v>삼평동 675</v>
+        <v>삼평동 662</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>SK엔크린 주유소 앞 횡단보도</v>
+        <v>시즌 앞 횡단보도</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -857,13 +857,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" t="str">
-        <v>판교역로</v>
+        <v>대왕판교로</v>
       </c>
       <c r="C11" t="str">
-        <v>25-성남시-7</v>
+        <v>25-성남시-8</v>
       </c>
       <c r="D11" t="str">
         <v>양호</v>
@@ -905,13 +905,13 @@
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v>삼평동 662</v>
+        <v>삼평동 663</v>
       </c>
       <c r="R11" t="str">
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>시즌 앞 횡단보도</v>
+        <v>스타벅스 앞 횡단보도</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -919,13 +919,13 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" t="str">
-        <v>대왕판교로</v>
+        <v>판교역로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-성남시-8</v>
+        <v>25-성남시-9</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
@@ -967,13 +967,13 @@
         <v/>
       </c>
       <c r="Q12" t="str">
-        <v>삼평동 663</v>
+        <v>삼평동 651</v>
       </c>
       <c r="R12" t="str">
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>스타벅스 앞 횡단보도</v>
+        <v>풍류더블랙 앞 도로</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -981,13 +981,13 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" t="str">
         <v>판교역로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-성남시-9</v>
+        <v>25-성남시-10</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
@@ -1029,13 +1029,13 @@
         <v/>
       </c>
       <c r="Q13" t="str">
-        <v>삼평동 651</v>
+        <v>백현동 537-1</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>풍류더블랙 앞 도로</v>
+        <v>판교역 #3번출구 앞 도로</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1043,13 +1043,13 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" t="str">
-        <v>판교역로</v>
+        <v>서현로</v>
       </c>
       <c r="C14" t="str">
-        <v>25-성남시-10</v>
+        <v>25-성남시-11</v>
       </c>
       <c r="D14" t="str">
         <v>양호</v>
@@ -1088,16 +1088,16 @@
         <v>일반</v>
       </c>
       <c r="P14" t="str">
-        <v/>
+        <v>침하 3cm</v>
       </c>
       <c r="Q14" t="str">
-        <v>백현동 537-1</v>
+        <v>백현동 529-2</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>판교역 #3번출구 앞 도로</v>
+        <v>낙생육교 앞 도로</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1105,13 +1105,13 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" t="str">
         <v>서현로</v>
       </c>
       <c r="C15" t="str">
-        <v>25-성남시-11</v>
+        <v>25-성남시-12</v>
       </c>
       <c r="D15" t="str">
         <v>양호</v>
@@ -1150,7 +1150,7 @@
         <v>일반</v>
       </c>
       <c r="P15" t="str">
-        <v>침하 3cm</v>
+        <v/>
       </c>
       <c r="Q15" t="str">
         <v>백현동 529-2</v>
@@ -1167,13 +1167,13 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="str">
-        <v>서현로</v>
+        <v>동판교역로</v>
       </c>
       <c r="C16" t="str">
-        <v>25-성남시-12</v>
+        <v>25-성남시-13</v>
       </c>
       <c r="D16" t="str">
         <v>양호</v>
@@ -1215,13 +1215,13 @@
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v>백현동 529-2</v>
+        <v>백현동 556-3</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>낙생육교 앞 도로</v>
+        <v>잿넘어육교 도로</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1229,13 +1229,13 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" t="str">
-        <v>동판교역로</v>
+        <v>판교역로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-성남시-13</v>
+        <v>25-성남시-14</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
@@ -1277,13 +1277,13 @@
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v>백현동 556-3</v>
+        <v>백현동 558-5</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>잿넘어육교 도로</v>
+        <v>신백현초등학교 앞 도로</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1291,13 +1291,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" t="str">
         <v>판교역로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-성남시-14</v>
+        <v>25-성남시-15</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
@@ -1339,13 +1339,13 @@
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v>백현동 558-5</v>
+        <v>백현동 560</v>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>신백현초등학교 앞 도로</v>
+        <v>블레도르 베이커리 앞 도로</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" t="str">
         <v>판교역로</v>
       </c>
       <c r="C19" t="str">
-        <v>25-성남시-15</v>
+        <v>25-성남시-16</v>
       </c>
       <c r="D19" t="str">
         <v>양호</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v>백현동 560</v>
+        <v>백현동 564-5</v>
       </c>
       <c r="R19" t="str">
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>블레도르 베이커리 앞 도로</v>
+        <v>세븐일레븐 앞 도로</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1415,13 +1415,13 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" t="str">
         <v>판교역로</v>
       </c>
       <c r="C20" t="str">
-        <v>25-성남시-16</v>
+        <v>25-성남시-17</v>
       </c>
       <c r="D20" t="str">
         <v>양호</v>
@@ -1463,13 +1463,13 @@
         <v/>
       </c>
       <c r="Q20" t="str">
-        <v>백현동 564-5</v>
+        <v>백현동 577-8</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>세븐일레븐 앞 도로</v>
+        <v>연남도토리 떡갈비 앞 횡단보도</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1477,13 +1477,13 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21" t="str">
-        <v>판교역로</v>
+        <v>분당수서로</v>
       </c>
       <c r="C21" t="str">
-        <v>25-성남시-17</v>
+        <v>25-성남시-18</v>
       </c>
       <c r="D21" t="str">
         <v>양호</v>
@@ -1525,33 +1525,34 @@
         <v/>
       </c>
       <c r="Q21" t="str">
-        <v>백현동 577-8</v>
+        <v>정자동 99-1</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>연남도토리 떡갈비 앞 횡단보도</v>
+        <v>잡월드사거리 도로</v>
       </c>
       <c r="T21" t="str">
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" xml:space="preserve">
       <c r="A22">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" t="str">
         <v>분당수서로</v>
       </c>
       <c r="C22" t="str">
-        <v>25-성남시-18</v>
+        <v>25-성남시-19</v>
       </c>
       <c r="D22" t="str">
         <v>양호</v>
       </c>
-      <c r="E22" t="str">
-        <v>거북등</v>
+      <c r="E22" t="str" xml:space="preserve">
+        <v xml:space="preserve">횡균열_x000d_
+종균열</v>
       </c>
       <c r="F22" t="str">
         <v>건조</v>
@@ -1566,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1578,13 +1579,13 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O22" t="str">
         <v>일반</v>
       </c>
       <c r="P22" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q22" t="str">
         <v>정자동 99-1</v>
@@ -1599,395 +1600,395 @@
         <v/>
       </c>
     </row>
-    <row r="23" xml:space="preserve">
+    <row r="23">
       <c r="A23">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" t="str">
-        <v>분당수서로</v>
+        <v>성남대로</v>
       </c>
       <c r="C23" t="str">
-        <v>25-성남시-19</v>
+        <v>25-성남시-20</v>
       </c>
       <c r="D23" t="str">
         <v>양호</v>
       </c>
-      <c r="E23" t="str" xml:space="preserve">
+      <c r="E23" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F23" t="str">
+        <v>건조</v>
+      </c>
+      <c r="G23" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H23" t="str">
+        <v>-</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>4</v>
+      </c>
+      <c r="O23" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v>백궁삼거리</v>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
+        <v>궁내교 앞 도로</v>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C24" t="str">
+        <v>25-성남시-21</v>
+      </c>
+      <c r="D24" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E24" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F24" t="str">
+        <v>건조</v>
+      </c>
+      <c r="G24" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H24" t="str">
+        <v>-</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>4</v>
+      </c>
+      <c r="O24" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P24" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>백궁삼거리</v>
+      </c>
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str">
+        <v>백궁삼거리 도로</v>
+      </c>
+      <c r="T24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C25" t="str">
+        <v>25-성남시-22</v>
+      </c>
+      <c r="D25" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E25" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F25" t="str">
+        <v>건조</v>
+      </c>
+      <c r="G25" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H25" t="str">
+        <v>-</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>4</v>
+      </c>
+      <c r="O25" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v>정자동 7</v>
+      </c>
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <v>한컴아카데미 맞음편 도로</v>
+      </c>
+      <c r="T25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C26" t="str">
+        <v>25-성남시-23</v>
+      </c>
+      <c r="D26" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E26" t="str">
+        <v>-</v>
+      </c>
+      <c r="F26" t="str">
+        <v>건조</v>
+      </c>
+      <c r="G26" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H26" t="str">
+        <v>-</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P26" t="str">
+        <v>보도침하3cm</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>정자동 7</v>
+      </c>
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str">
+        <v>궁내교 현판 앞 보도</v>
+      </c>
+      <c r="T26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C27" t="str">
+        <v>25-성남시-24</v>
+      </c>
+      <c r="D27" t="str">
+        <v>보통</v>
+      </c>
+      <c r="E27" t="str">
+        <v>-</v>
+      </c>
+      <c r="F27" t="str">
+        <v>건조</v>
+      </c>
+      <c r="G27" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H27" t="str">
+        <v>-</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>4</v>
+      </c>
+      <c r="O27" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P27" t="str">
+        <v>보도침하5cm</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>정자동 15-4</v>
+      </c>
+      <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27" t="str">
+        <v>가로등118(성남대로376) 보도</v>
+      </c>
+      <c r="T27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C28" t="str">
+        <v>25-성남시-25</v>
+      </c>
+      <c r="D28" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E28" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F28" t="str">
+        <v>건조</v>
+      </c>
+      <c r="G28" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H28" t="str">
+        <v>-</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>4</v>
+      </c>
+      <c r="O28" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v>정자동 15-4</v>
+      </c>
+      <c r="R28" t="str">
+        <v/>
+      </c>
+      <c r="S28" t="str">
+        <v>가로등118(성남대로376) 도로</v>
+      </c>
+      <c r="T28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C29" t="str">
+        <v>25-성남시-26</v>
+      </c>
+      <c r="D29" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E29" t="str" xml:space="preserve">
         <v xml:space="preserve">횡균열_x000d_
 종균열</v>
       </c>
-      <c r="F23" t="str">
-        <v>건조</v>
-      </c>
-      <c r="G23" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H23" t="str">
-        <v>-</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>1</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>2</v>
-      </c>
-      <c r="O23" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P23" t="str">
-        <v>5cm이하 침하</v>
-      </c>
-      <c r="Q23" t="str">
-        <v>정자동 99-1</v>
-      </c>
-      <c r="R23" t="str">
-        <v/>
-      </c>
-      <c r="S23" t="str">
-        <v>잡월드사거리 도로</v>
-      </c>
-      <c r="T23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>20</v>
-      </c>
-      <c r="B24" t="str">
-        <v>성남대로</v>
-      </c>
-      <c r="C24" t="str">
-        <v>25-성남시-20</v>
-      </c>
-      <c r="D24" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E24" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F24" t="str">
-        <v>건조</v>
-      </c>
-      <c r="G24" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H24" t="str">
-        <v>-</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>3</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>1</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>4</v>
-      </c>
-      <c r="O24" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P24" t="str">
-        <v/>
-      </c>
-      <c r="Q24" t="str">
-        <v>백궁삼거리</v>
-      </c>
-      <c r="R24" t="str">
-        <v/>
-      </c>
-      <c r="S24" t="str">
-        <v>궁내교 앞 도로</v>
-      </c>
-      <c r="T24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>21</v>
-      </c>
-      <c r="B25" t="str">
-        <v>성남대로</v>
-      </c>
-      <c r="C25" t="str">
-        <v>25-성남시-21</v>
-      </c>
-      <c r="D25" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E25" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F25" t="str">
-        <v>건조</v>
-      </c>
-      <c r="G25" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H25" t="str">
-        <v>-</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>3</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>1</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>4</v>
-      </c>
-      <c r="O25" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P25" t="str">
-        <v>5cm이하 침하</v>
-      </c>
-      <c r="Q25" t="str">
-        <v>백궁삼거리</v>
-      </c>
-      <c r="R25" t="str">
-        <v/>
-      </c>
-      <c r="S25" t="str">
-        <v>백궁삼거리 도로</v>
-      </c>
-      <c r="T25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>22</v>
-      </c>
-      <c r="B26" t="str">
-        <v>성남대로</v>
-      </c>
-      <c r="C26" t="str">
-        <v>25-성남시-22</v>
-      </c>
-      <c r="D26" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E26" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F26" t="str">
-        <v>건조</v>
-      </c>
-      <c r="G26" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H26" t="str">
-        <v>-</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>3</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>1</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>4</v>
-      </c>
-      <c r="O26" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P26" t="str">
-        <v/>
-      </c>
-      <c r="Q26" t="str">
-        <v>정자동 7</v>
-      </c>
-      <c r="R26" t="str">
-        <v/>
-      </c>
-      <c r="S26" t="str">
-        <v>한컴아카데미 맞음편 도로</v>
-      </c>
-      <c r="T26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>23</v>
-      </c>
-      <c r="B27" t="str">
-        <v>성남대로</v>
-      </c>
-      <c r="C27" t="str">
-        <v>25-성남시-23</v>
-      </c>
-      <c r="D27" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E27" t="str">
-        <v>-</v>
-      </c>
-      <c r="F27" t="str">
-        <v>건조</v>
-      </c>
-      <c r="G27" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H27" t="str">
-        <v>-</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>1</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <v>1</v>
-      </c>
-      <c r="O27" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P27" t="str">
-        <v>보도침하3cm</v>
-      </c>
-      <c r="Q27" t="str">
-        <v>정자동 7</v>
-      </c>
-      <c r="R27" t="str">
-        <v/>
-      </c>
-      <c r="S27" t="str">
-        <v>궁내교 현판 앞 보도</v>
-      </c>
-      <c r="T27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>24</v>
-      </c>
-      <c r="B28" t="str">
-        <v>성남대로</v>
-      </c>
-      <c r="C28" t="str">
-        <v>25-성남시-24</v>
-      </c>
-      <c r="D28" t="str">
-        <v>보통</v>
-      </c>
-      <c r="E28" t="str">
-        <v>-</v>
-      </c>
-      <c r="F28" t="str">
-        <v>건조</v>
-      </c>
-      <c r="G28" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H28" t="str">
-        <v>-</v>
-      </c>
-      <c r="I28">
-        <v>3</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>4</v>
-      </c>
-      <c r="O28" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P28" t="str">
-        <v>보도침하5cm</v>
-      </c>
-      <c r="Q28" t="str">
-        <v>정자동 15-4</v>
-      </c>
-      <c r="R28" t="str">
-        <v/>
-      </c>
-      <c r="S28" t="str">
-        <v>가로등118(성남대로376) 보도</v>
-      </c>
-      <c r="T28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>25</v>
-      </c>
-      <c r="B29" t="str">
-        <v>성남대로</v>
-      </c>
-      <c r="C29" t="str">
-        <v>25-성남시-25</v>
-      </c>
-      <c r="D29" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E29" t="str">
-        <v>거북등</v>
-      </c>
       <c r="F29" t="str">
         <v>건조</v>
       </c>
@@ -2001,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -2013,292 +2014,292 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O29" t="str">
         <v>일반</v>
       </c>
       <c r="P29" t="str">
-        <v/>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q29" t="str">
-        <v>정자동 15-4</v>
+        <v>궁내사거리</v>
       </c>
       <c r="R29" t="str">
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>가로등118(성남대로376) 도로</v>
+        <v>궁내사거리 앞 도로</v>
       </c>
       <c r="T29" t="str">
         <v/>
       </c>
     </row>
-    <row r="30" xml:space="preserve">
+    <row r="30">
       <c r="A30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" t="str">
         <v>성남대로</v>
       </c>
       <c r="C30" t="str">
-        <v>25-성남시-26</v>
+        <v>25-성남시-27</v>
       </c>
       <c r="D30" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E30" t="str" xml:space="preserve">
+        <v>보통</v>
+      </c>
+      <c r="E30" t="str">
+        <v>-</v>
+      </c>
+      <c r="F30" t="str">
+        <v>건조</v>
+      </c>
+      <c r="G30" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H30" t="str">
+        <v>-</v>
+      </c>
+      <c r="I30">
+        <v>3</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>4</v>
+      </c>
+      <c r="O30" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P30" t="str">
+        <v>보도침하5cm</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>정자동 17-2</v>
+      </c>
+      <c r="R30" t="str">
+        <v/>
+      </c>
+      <c r="S30" t="str">
+        <v>정자역 #5번출구 앞 보도</v>
+      </c>
+      <c r="T30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C31" t="str">
+        <v>25-성남시-28</v>
+      </c>
+      <c r="D31" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E31" t="str">
+        <v>종균열</v>
+      </c>
+      <c r="F31" t="str">
+        <v>건조</v>
+      </c>
+      <c r="G31" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H31" t="str">
+        <v>-</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>2</v>
+      </c>
+      <c r="O31" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
+        <v>정자동 17-2</v>
+      </c>
+      <c r="R31" t="str">
+        <v/>
+      </c>
+      <c r="S31" t="str">
+        <v>정자역 #5번출구 앞 도로</v>
+      </c>
+      <c r="T31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C32" t="str">
+        <v>25-성남시-29</v>
+      </c>
+      <c r="D32" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E32" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F32" t="str">
+        <v>건조</v>
+      </c>
+      <c r="G32" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H32" t="str">
+        <v>-</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>4</v>
+      </c>
+      <c r="O32" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P32" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>정자동 26-1</v>
+      </c>
+      <c r="R32" t="str">
+        <v/>
+      </c>
+      <c r="S32" t="str">
+        <v>신기교 앞 횡단보도</v>
+      </c>
+      <c r="T32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C33" t="str">
+        <v>25-성남시-30</v>
+      </c>
+      <c r="D33" t="str">
+        <v>보통</v>
+      </c>
+      <c r="E33" t="str">
+        <v>-</v>
+      </c>
+      <c r="F33" t="str">
+        <v>건조</v>
+      </c>
+      <c r="G33" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H33" t="str">
+        <v>-</v>
+      </c>
+      <c r="I33">
+        <v>3</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>4</v>
+      </c>
+      <c r="O33" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P33" t="str">
+        <v>보도침하8cm</v>
+      </c>
+      <c r="Q33" t="str">
+        <v>정자동 26-1</v>
+      </c>
+      <c r="R33" t="str">
+        <v/>
+      </c>
+      <c r="S33" t="str">
+        <v>정자역 버스정류장 보도</v>
+      </c>
+      <c r="T33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34">
+        <v>31</v>
+      </c>
+      <c r="B34" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C34" t="str">
+        <v>25-성남시-31</v>
+      </c>
+      <c r="D34" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E34" t="str" xml:space="preserve">
         <v xml:space="preserve">횡균열_x000d_
 종균열</v>
       </c>
-      <c r="F30" t="str">
-        <v>건조</v>
-      </c>
-      <c r="G30" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H30" t="str">
-        <v>-</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>1</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>2</v>
-      </c>
-      <c r="O30" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P30" t="str">
-        <v>5cm이하 침하</v>
-      </c>
-      <c r="Q30" t="str">
-        <v>궁내사거리</v>
-      </c>
-      <c r="R30" t="str">
-        <v/>
-      </c>
-      <c r="S30" t="str">
-        <v>궁내사거리 앞 도로</v>
-      </c>
-      <c r="T30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>27</v>
-      </c>
-      <c r="B31" t="str">
-        <v>성남대로</v>
-      </c>
-      <c r="C31" t="str">
-        <v>25-성남시-27</v>
-      </c>
-      <c r="D31" t="str">
-        <v>보통</v>
-      </c>
-      <c r="E31" t="str">
-        <v>-</v>
-      </c>
-      <c r="F31" t="str">
-        <v>건조</v>
-      </c>
-      <c r="G31" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H31" t="str">
-        <v>-</v>
-      </c>
-      <c r="I31">
-        <v>3</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>1</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>4</v>
-      </c>
-      <c r="O31" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P31" t="str">
-        <v>보도침하5cm</v>
-      </c>
-      <c r="Q31" t="str">
-        <v>정자동 17-2</v>
-      </c>
-      <c r="R31" t="str">
-        <v/>
-      </c>
-      <c r="S31" t="str">
-        <v>정자역 #5번출구 앞 보도</v>
-      </c>
-      <c r="T31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>28</v>
-      </c>
-      <c r="B32" t="str">
-        <v>성남대로</v>
-      </c>
-      <c r="C32" t="str">
-        <v>25-성남시-28</v>
-      </c>
-      <c r="D32" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E32" t="str">
-        <v>종균열</v>
-      </c>
-      <c r="F32" t="str">
-        <v>건조</v>
-      </c>
-      <c r="G32" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H32" t="str">
-        <v>-</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>1</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>1</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>2</v>
-      </c>
-      <c r="O32" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P32" t="str">
-        <v/>
-      </c>
-      <c r="Q32" t="str">
-        <v>정자동 17-2</v>
-      </c>
-      <c r="R32" t="str">
-        <v/>
-      </c>
-      <c r="S32" t="str">
-        <v>정자역 #5번출구 앞 도로</v>
-      </c>
-      <c r="T32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>29</v>
-      </c>
-      <c r="B33" t="str">
-        <v>성남대로</v>
-      </c>
-      <c r="C33" t="str">
-        <v>25-성남시-29</v>
-      </c>
-      <c r="D33" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E33" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F33" t="str">
-        <v>건조</v>
-      </c>
-      <c r="G33" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H33" t="str">
-        <v>-</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>3</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>1</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>4</v>
-      </c>
-      <c r="O33" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P33" t="str">
-        <v>5cm이하 침하</v>
-      </c>
-      <c r="Q33" t="str">
-        <v>정자동 26-1</v>
-      </c>
-      <c r="R33" t="str">
-        <v/>
-      </c>
-      <c r="S33" t="str">
-        <v>신기교 앞 횡단보도</v>
-      </c>
-      <c r="T33" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>30</v>
-      </c>
-      <c r="B34" t="str">
-        <v>성남대로</v>
-      </c>
-      <c r="C34" t="str">
-        <v>25-성남시-30</v>
-      </c>
-      <c r="D34" t="str">
-        <v>보통</v>
-      </c>
-      <c r="E34" t="str">
-        <v>-</v>
-      </c>
       <c r="F34" t="str">
         <v>건조</v>
       </c>
@@ -2309,10 +2310,10 @@
         <v>-</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -2324,106 +2325,106 @@
         <v>0</v>
       </c>
       <c r="N34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O34" t="str">
         <v>일반</v>
       </c>
       <c r="P34" t="str">
-        <v>보도침하8cm</v>
+        <v/>
       </c>
       <c r="Q34" t="str">
-        <v>정자동 26-1</v>
+        <v>정자동 156-1</v>
       </c>
       <c r="R34" t="str">
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>정자역 버스정류장 보도</v>
+        <v>파리바게트 앞 도로</v>
       </c>
       <c r="T34" t="str">
         <v/>
       </c>
     </row>
-    <row r="35" xml:space="preserve">
+    <row r="35">
       <c r="A35">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B35" t="str">
         <v>성남대로</v>
       </c>
       <c r="C35" t="str">
-        <v>25-성남시-31</v>
+        <v>25-성남시-32</v>
       </c>
       <c r="D35" t="str">
         <v>양호</v>
       </c>
-      <c r="E35" t="str" xml:space="preserve">
+      <c r="E35" t="str">
+        <v>횡균열</v>
+      </c>
+      <c r="F35" t="str">
+        <v>건조</v>
+      </c>
+      <c r="G35" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H35" t="str">
+        <v>-</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>2</v>
+      </c>
+      <c r="O35" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
+        <v>정자동 156-1</v>
+      </c>
+      <c r="R35" t="str">
+        <v/>
+      </c>
+      <c r="S35" t="str">
+        <v>서현실비 맞음편 도로</v>
+      </c>
+      <c r="T35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C36" t="str">
+        <v>25-성남시-33</v>
+      </c>
+      <c r="D36" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E36" t="str" xml:space="preserve">
         <v xml:space="preserve">횡균열_x000d_
 종균열</v>
       </c>
-      <c r="F35" t="str">
-        <v>건조</v>
-      </c>
-      <c r="G35" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H35" t="str">
-        <v>-</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>1</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>2</v>
-      </c>
-      <c r="O35" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P35" t="str">
-        <v/>
-      </c>
-      <c r="Q35" t="str">
-        <v>정자동 156-1</v>
-      </c>
-      <c r="R35" t="str">
-        <v/>
-      </c>
-      <c r="S35" t="str">
-        <v>파리바게트 앞 도로</v>
-      </c>
-      <c r="T35" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>32</v>
-      </c>
-      <c r="B36" t="str">
-        <v>성남대로</v>
-      </c>
-      <c r="C36" t="str">
-        <v>25-성남시-32</v>
-      </c>
-      <c r="D36" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E36" t="str">
-        <v>횡균열</v>
-      </c>
       <c r="F36" t="str">
         <v>건조</v>
       </c>
@@ -2458,13 +2459,13 @@
         <v/>
       </c>
       <c r="Q36" t="str">
-        <v>정자동 156-1</v>
+        <v>정자동 156-3</v>
       </c>
       <c r="R36" t="str">
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>서현실비 맞음편 도로</v>
+        <v>나드림요양원 앞 도로</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2472,13 +2473,13 @@
     </row>
     <row r="37" xml:space="preserve">
       <c r="A37">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" t="str">
         <v>성남대로</v>
       </c>
       <c r="C37" t="str">
-        <v>25-성남시-33</v>
+        <v>25-성남시-34</v>
       </c>
       <c r="D37" t="str">
         <v>양호</v>
@@ -2527,7 +2528,7 @@
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>나드림요양원 앞 도로</v>
+        <v>가로등103(성남대로320) 도로</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2535,13 +2536,13 @@
     </row>
     <row r="38" xml:space="preserve">
       <c r="A38">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B38" t="str">
         <v>성남대로</v>
       </c>
       <c r="C38" t="str">
-        <v>25-성남시-34</v>
+        <v>25-성남시-35</v>
       </c>
       <c r="D38" t="str">
         <v>양호</v>
@@ -2584,283 +2585,283 @@
         <v/>
       </c>
       <c r="Q38" t="str">
-        <v>정자동 156-3</v>
+        <v>정자동 154-1</v>
       </c>
       <c r="R38" t="str">
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>가로등103(성남대로320) 도로</v>
+        <v>타임브릿지 앞 도로</v>
       </c>
       <c r="T38" t="str">
         <v/>
       </c>
     </row>
-    <row r="39" xml:space="preserve">
+    <row r="39">
       <c r="A39">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B39" t="str">
         <v>성남대로</v>
       </c>
       <c r="C39" t="str">
-        <v>25-성남시-35</v>
+        <v>25-성남시-36</v>
       </c>
       <c r="D39" t="str">
         <v>양호</v>
       </c>
-      <c r="E39" t="str" xml:space="preserve">
+      <c r="E39" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F39" t="str">
+        <v>건조</v>
+      </c>
+      <c r="G39" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H39" t="str">
+        <v>-</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>4</v>
+      </c>
+      <c r="O39" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
+        <v>금곡교사거리</v>
+      </c>
+      <c r="R39" t="str">
+        <v/>
+      </c>
+      <c r="S39" t="str">
+        <v>금곡교사거리 도로</v>
+      </c>
+      <c r="T39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>37</v>
+      </c>
+      <c r="B40" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C40" t="str">
+        <v>25-성남시-37</v>
+      </c>
+      <c r="D40" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E40" t="str">
+        <v>종균열</v>
+      </c>
+      <c r="F40" t="str">
+        <v>건조</v>
+      </c>
+      <c r="G40" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H40" t="str">
+        <v>-</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>2</v>
+      </c>
+      <c r="O40" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+      <c r="Q40" t="str">
+        <v>정자동 168-1</v>
+      </c>
+      <c r="R40" t="str">
+        <v/>
+      </c>
+      <c r="S40" t="str">
+        <v>GS25편의점 앞 도로</v>
+      </c>
+      <c r="T40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C41" t="str">
+        <v>25-성남시-38</v>
+      </c>
+      <c r="D41" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E41" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F41" t="str">
+        <v>건조</v>
+      </c>
+      <c r="G41" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H41" t="str">
+        <v>-</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>3</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>4</v>
+      </c>
+      <c r="O41" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41" t="str">
+        <v>정자동 168-1</v>
+      </c>
+      <c r="R41" t="str">
+        <v/>
+      </c>
+      <c r="S41" t="str">
+        <v>제빵소 앞 도로</v>
+      </c>
+      <c r="T41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>39</v>
+      </c>
+      <c r="B42" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C42" t="str">
+        <v>25-성남시-39</v>
+      </c>
+      <c r="D42" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E42" t="str">
+        <v>종균열</v>
+      </c>
+      <c r="F42" t="str">
+        <v>건조</v>
+      </c>
+      <c r="G42" t="str">
+        <v>13.5</v>
+      </c>
+      <c r="H42" t="str">
+        <v>-</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>2</v>
+      </c>
+      <c r="O42" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+      <c r="Q42" t="str">
+        <v>정자동 168-1</v>
+      </c>
+      <c r="R42" t="str">
+        <v/>
+      </c>
+      <c r="S42" t="str">
+        <v>상록지하보도 앞 도로</v>
+      </c>
+      <c r="T42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43">
+        <v>40</v>
+      </c>
+      <c r="B43" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C43" t="str">
+        <v>25-성남시-40</v>
+      </c>
+      <c r="D43" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E43" t="str" xml:space="preserve">
         <v xml:space="preserve">횡균열_x000d_
 종균열</v>
       </c>
-      <c r="F39" t="str">
-        <v>건조</v>
-      </c>
-      <c r="G39" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H39" t="str">
-        <v>-</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>1</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39">
-        <v>1</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>2</v>
-      </c>
-      <c r="O39" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P39" t="str">
-        <v/>
-      </c>
-      <c r="Q39" t="str">
-        <v>정자동 154-1</v>
-      </c>
-      <c r="R39" t="str">
-        <v/>
-      </c>
-      <c r="S39" t="str">
-        <v>타임브릿지 앞 도로</v>
-      </c>
-      <c r="T39" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>36</v>
-      </c>
-      <c r="B40" t="str">
-        <v>성남대로</v>
-      </c>
-      <c r="C40" t="str">
-        <v>25-성남시-36</v>
-      </c>
-      <c r="D40" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E40" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F40" t="str">
-        <v>건조</v>
-      </c>
-      <c r="G40" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H40" t="str">
-        <v>-</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>3</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>1</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>4</v>
-      </c>
-      <c r="O40" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P40" t="str">
-        <v/>
-      </c>
-      <c r="Q40" t="str">
-        <v>금곡교사거리</v>
-      </c>
-      <c r="R40" t="str">
-        <v/>
-      </c>
-      <c r="S40" t="str">
-        <v>금곡교사거리 도로</v>
-      </c>
-      <c r="T40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>37</v>
-      </c>
-      <c r="B41" t="str">
-        <v>성남대로</v>
-      </c>
-      <c r="C41" t="str">
-        <v>25-성남시-37</v>
-      </c>
-      <c r="D41" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E41" t="str">
-        <v>종균열</v>
-      </c>
-      <c r="F41" t="str">
-        <v>건조</v>
-      </c>
-      <c r="G41" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H41" t="str">
-        <v>-</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>1</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>1</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>2</v>
-      </c>
-      <c r="O41" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P41" t="str">
-        <v/>
-      </c>
-      <c r="Q41" t="str">
-        <v>정자동 168-1</v>
-      </c>
-      <c r="R41" t="str">
-        <v/>
-      </c>
-      <c r="S41" t="str">
-        <v>GS25편의점 앞 도로</v>
-      </c>
-      <c r="T41" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>38</v>
-      </c>
-      <c r="B42" t="str">
-        <v>성남대로</v>
-      </c>
-      <c r="C42" t="str">
-        <v>25-성남시-38</v>
-      </c>
-      <c r="D42" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E42" t="str">
-        <v>거북등</v>
-      </c>
-      <c r="F42" t="str">
-        <v>건조</v>
-      </c>
-      <c r="G42" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H42" t="str">
-        <v>-</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>3</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>1</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <v>4</v>
-      </c>
-      <c r="O42" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P42" t="str">
-        <v/>
-      </c>
-      <c r="Q42" t="str">
-        <v>정자동 168-1</v>
-      </c>
-      <c r="R42" t="str">
-        <v/>
-      </c>
-      <c r="S42" t="str">
-        <v>제빵소 앞 도로</v>
-      </c>
-      <c r="T42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>39</v>
-      </c>
-      <c r="B43" t="str">
-        <v>성남대로</v>
-      </c>
-      <c r="C43" t="str">
-        <v>25-성남시-39</v>
-      </c>
-      <c r="D43" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E43" t="str">
-        <v>종균열</v>
-      </c>
       <c r="F43" t="str">
         <v>건조</v>
       </c>
@@ -2895,34 +2896,33 @@
         <v/>
       </c>
       <c r="Q43" t="str">
-        <v>정자동 168-1</v>
+        <v>정자동 169-1</v>
       </c>
       <c r="R43" t="str">
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>상록지하보도 앞 도로</v>
+        <v>아데나펠리스 버스정류장 앞 도로</v>
       </c>
       <c r="T43" t="str">
         <v/>
       </c>
     </row>
-    <row r="44" xml:space="preserve">
+    <row r="44">
       <c r="A44">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B44" t="str">
         <v>성남대로</v>
       </c>
       <c r="C44" t="str">
-        <v>25-성남시-40</v>
+        <v>25-성남시-41</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
       </c>
-      <c r="E44" t="str" xml:space="preserve">
-        <v xml:space="preserve">횡균열_x000d_
-종균열</v>
+      <c r="E44" t="str">
+        <v>-</v>
       </c>
       <c r="F44" t="str">
         <v>건조</v>
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -2949,13 +2949,13 @@
         <v>0</v>
       </c>
       <c r="N44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O44" t="str">
         <v>일반</v>
       </c>
       <c r="P44" t="str">
-        <v/>
+        <v>침하 3.5cm</v>
       </c>
       <c r="Q44" t="str">
         <v>정자동 169-1</v>
@@ -2964,7 +2964,7 @@
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>아데나펠리스 버스정류장 앞 도로</v>
+        <v>스타벅스 맞음편 도로</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -2972,19 +2972,19 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B45" t="str">
         <v>성남대로</v>
       </c>
       <c r="C45" t="str">
-        <v>25-성남시-41</v>
+        <v>25-성남시-42</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
       </c>
       <c r="E45" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F45" t="str">
         <v>건조</v>
@@ -2999,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -3011,84 +3011,84 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O45" t="str">
         <v>일반</v>
       </c>
       <c r="P45" t="str">
-        <v>침하 3.5cm</v>
+        <v/>
       </c>
       <c r="Q45" t="str">
-        <v>정자동 169-1</v>
+        <v>불정교사거리</v>
       </c>
       <c r="R45" t="str">
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>스타벅스 맞음편 도로</v>
+        <v>불정교사거리 도로</v>
       </c>
       <c r="T45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>42</v>
+      <c r="A46" t="str">
+        <v>26-01</v>
       </c>
       <c r="B46" t="str">
-        <v>성남대로</v>
+        <v>판교로</v>
       </c>
       <c r="C46" t="str">
-        <v>25-성남시-42</v>
+        <v>26-성남시-01</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
       </c>
       <c r="E46" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F46" t="str">
-        <v>건조</v>
+        <v>양호</v>
       </c>
       <c r="G46" t="str">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="H46" t="str">
         <v>-</v>
       </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>3</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>1</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <v>4</v>
+      <c r="I46" t="str">
+        <v>0</v>
+      </c>
+      <c r="J46" t="str">
+        <v>1</v>
+      </c>
+      <c r="K46" t="str">
+        <v>0</v>
+      </c>
+      <c r="L46" t="str">
+        <v>1</v>
+      </c>
+      <c r="M46" t="str">
+        <v>0</v>
+      </c>
+      <c r="N46" t="str">
+        <v>2</v>
       </c>
       <c r="O46" t="str">
         <v>일반</v>
       </c>
       <c r="P46" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="Q46" t="str">
-        <v>불정교사거리</v>
+        <v>삼평동702</v>
       </c>
       <c r="R46" t="str">
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>불정교사거리 도로</v>
+        <v>휴세코 앞  횐단보도(판교로333)</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3096,19 +3096,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>26-01</v>
+        <v>26-02</v>
       </c>
       <c r="B47" t="str">
         <v>판교로</v>
       </c>
       <c r="C47" t="str">
-        <v>26-성남시-01</v>
+        <v>26-성남시-02</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
       </c>
       <c r="E47" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F47" t="str">
         <v>양호</v>
@@ -3144,13 +3144,13 @@
         <v>-</v>
       </c>
       <c r="Q47" t="str">
-        <v>삼평동702</v>
+        <v>삼평동689-1</v>
       </c>
       <c r="R47" t="str">
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>휴세코 앞  횐단보도(판교로333)</v>
+        <v>차그룹컨소시업 버스정류장 앞 도로</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3158,19 +3158,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>26-02</v>
+        <v>26-03</v>
       </c>
       <c r="B48" t="str">
         <v>판교로</v>
       </c>
       <c r="C48" t="str">
-        <v>26-성남시-02</v>
+        <v>26-성남시-03</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
       </c>
       <c r="E48" t="str">
-        <v>종균열</v>
+        <v>양호</v>
       </c>
       <c r="F48" t="str">
         <v>양호</v>
@@ -3185,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="str">
         <v>0</v>
@@ -3197,22 +3197,22 @@
         <v>0</v>
       </c>
       <c r="N48" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O48" t="str">
         <v>일반</v>
       </c>
       <c r="P48" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q48" t="str">
-        <v>삼평동689-1</v>
+        <v>삼평동688-3</v>
       </c>
       <c r="R48" t="str">
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>차그룹컨소시업 버스정류장 앞 도로</v>
+        <v>한국무역정보통신 버스정류장 앞도로</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3220,19 +3220,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>26-03</v>
+        <v>26-04</v>
       </c>
       <c r="B49" t="str">
-        <v>판교로</v>
+        <v>판교역로</v>
       </c>
       <c r="C49" t="str">
-        <v>26-성남시-03</v>
+        <v>26-성남시-04</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
       </c>
       <c r="E49" t="str">
-        <v>양호</v>
+        <v>거북등</v>
       </c>
       <c r="F49" t="str">
         <v>양호</v>
@@ -3247,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K49" t="str">
         <v>0</v>
@@ -3259,22 +3259,22 @@
         <v>0</v>
       </c>
       <c r="N49" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O49" t="str">
         <v>일반</v>
       </c>
       <c r="P49" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q49" t="str">
-        <v>삼평동688-3</v>
+        <v>삼평동679</v>
       </c>
       <c r="R49" t="str">
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>한국무역정보통신 버스정류장 앞도로</v>
+        <v>삼환하이펙스 B동 코이라멘_판교점 앞 횡단보도(판교역로230)</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3282,19 +3282,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>26-04</v>
+        <v>26-05</v>
       </c>
       <c r="B50" t="str">
-        <v>판교역로</v>
+        <v>대왕판교로</v>
       </c>
       <c r="C50" t="str">
-        <v>26-성남시-04</v>
+        <v>26-성남시-05</v>
       </c>
       <c r="D50" t="str">
         <v>양호</v>
       </c>
       <c r="E50" t="str">
-        <v>거북등</v>
+        <v>종,횡균열</v>
       </c>
       <c r="F50" t="str">
         <v>양호</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K50" t="str">
         <v>0</v>
@@ -3321,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="N50" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O50" t="str">
         <v>일반</v>
@@ -3330,13 +3330,13 @@
         <v>-</v>
       </c>
       <c r="Q50" t="str">
-        <v>삼평동679</v>
+        <v>삼평동673</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>삼환하이펙스 B동 코이라멘_판교점 앞 횡단보도(판교역로230)</v>
+        <v>솔리드카페 앞 도로(판교역로220)</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3344,19 +3344,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>26-05</v>
+        <v>26-06</v>
       </c>
       <c r="B51" t="str">
-        <v>대왕판교로</v>
+        <v>판교역로</v>
       </c>
       <c r="C51" t="str">
-        <v>26-성남시-05</v>
+        <v>26-성남시-06</v>
       </c>
       <c r="D51" t="str">
         <v>양호</v>
       </c>
       <c r="E51" t="str">
-        <v>종,횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F51" t="str">
         <v>양호</v>
@@ -3392,13 +3392,13 @@
         <v>-</v>
       </c>
       <c r="Q51" t="str">
-        <v>삼평동673</v>
+        <v>삼평동662</v>
       </c>
       <c r="R51" t="str">
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>솔리드카페 앞 도로(판교역로220)</v>
+        <v>판교타워 앞 도로(판교역로192번길16</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3406,19 +3406,19 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>26-06</v>
+        <v>26-07</v>
       </c>
       <c r="B52" t="str">
         <v>판교역로</v>
       </c>
       <c r="C52" t="str">
-        <v>26-성남시-06</v>
+        <v>26-성남시-07</v>
       </c>
       <c r="D52" t="str">
         <v>양호</v>
       </c>
       <c r="E52" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F52" t="str">
         <v>양호</v>
@@ -3433,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K52" t="str">
         <v>0</v>
@@ -3445,7 +3445,7 @@
         <v>0</v>
       </c>
       <c r="N52" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O52" t="str">
         <v>일반</v>
@@ -3454,13 +3454,13 @@
         <v>-</v>
       </c>
       <c r="Q52" t="str">
-        <v>삼평동662</v>
+        <v>백현동539</v>
       </c>
       <c r="R52" t="str">
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>판교타워 앞 도로(판교역로192번길16</v>
+        <v>판교공영주차장 앞 횡단보도(판교역로146번길8)</v>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -3468,13 +3468,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>26-07</v>
+        <v>26-08</v>
       </c>
       <c r="B53" t="str">
-        <v>판교역로</v>
+        <v>서현로</v>
       </c>
       <c r="C53" t="str">
-        <v>26-성남시-07</v>
+        <v>26-성남시-08</v>
       </c>
       <c r="D53" t="str">
         <v>양호</v>
@@ -3486,7 +3486,7 @@
         <v>양호</v>
       </c>
       <c r="G53" t="str">
-        <v>14.5</v>
+        <v>14-5</v>
       </c>
       <c r="H53" t="str">
         <v>-</v>
@@ -3516,13 +3516,13 @@
         <v>-</v>
       </c>
       <c r="Q53" t="str">
-        <v>백현동539</v>
+        <v>백현동554-3</v>
       </c>
       <c r="R53" t="str">
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>판교공영주차장 앞 횡단보도(판교역로146번길8)</v>
+        <v>낙생육교 버스정류장 앞 도로</v>
       </c>
       <c r="T53" t="str">
         <v/>
@@ -3530,13 +3530,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>26-08</v>
+        <v>26-09</v>
       </c>
       <c r="B54" t="str">
-        <v>서현로</v>
+        <v>동판교로</v>
       </c>
       <c r="C54" t="str">
-        <v>26-성남시-08</v>
+        <v>26-성남시-09</v>
       </c>
       <c r="D54" t="str">
         <v>양호</v>
@@ -3548,7 +3548,7 @@
         <v>양호</v>
       </c>
       <c r="G54" t="str">
-        <v>14-5</v>
+        <v>14.5</v>
       </c>
       <c r="H54" t="str">
         <v>-</v>
@@ -3578,13 +3578,13 @@
         <v>-</v>
       </c>
       <c r="Q54" t="str">
-        <v>백현동554-3</v>
+        <v>백현동556-3</v>
       </c>
       <c r="R54" t="str">
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>낙생육교 버스정류장 앞 도로</v>
+        <v>잿넘어육교 밑 도로</v>
       </c>
       <c r="T54" t="str">
         <v/>
@@ -3592,13 +3592,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>26-09</v>
+        <v>26-10</v>
       </c>
       <c r="B55" t="str">
-        <v>동판교로</v>
+        <v>판교역로</v>
       </c>
       <c r="C55" t="str">
-        <v>26-성남시-09</v>
+        <v>26-성남시-10</v>
       </c>
       <c r="D55" t="str">
         <v>양호</v>
@@ -3640,13 +3640,13 @@
         <v>-</v>
       </c>
       <c r="Q55" t="str">
-        <v>백현동556-3</v>
+        <v>백현동559</v>
       </c>
       <c r="R55" t="str">
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>잿넘어육교 밑 도로</v>
+        <v>신백현초등학교 병설유치원 앞 도로(판교역로14번길42)</v>
       </c>
       <c r="T55" t="str">
         <v/>
@@ -3654,19 +3654,19 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>26-10</v>
+        <v>26-11</v>
       </c>
       <c r="B56" t="str">
         <v>판교역로</v>
       </c>
       <c r="C56" t="str">
-        <v>26-성남시-10</v>
+        <v>26-성남시-11</v>
       </c>
       <c r="D56" t="str">
         <v>양호</v>
       </c>
       <c r="E56" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F56" t="str">
         <v>양호</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K56" t="str">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="N56" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O56" t="str">
         <v>일반</v>
@@ -3702,13 +3702,13 @@
         <v>-</v>
       </c>
       <c r="Q56" t="str">
-        <v>백현동559</v>
+        <v>백현동558</v>
       </c>
       <c r="R56" t="str">
         <v/>
       </c>
       <c r="S56" t="str">
-        <v>신백현초등학교 병설유치원 앞 도로(판교역로14번길42)</v>
+        <v>백현마을8단지 아파트 입구</v>
       </c>
       <c r="T56" t="str">
         <v/>
@@ -3716,19 +3716,19 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>26-11</v>
+        <v>26-12</v>
       </c>
       <c r="B57" t="str">
         <v>판교역로</v>
       </c>
       <c r="C57" t="str">
-        <v>26-성남시-11</v>
+        <v>26-성남시-12</v>
       </c>
       <c r="D57" t="str">
         <v>양호</v>
       </c>
       <c r="E57" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F57" t="str">
         <v>양호</v>
@@ -3743,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="J57" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K57" t="str">
         <v>0</v>
@@ -3755,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="N57" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O57" t="str">
         <v>일반</v>
@@ -3764,13 +3764,13 @@
         <v>-</v>
       </c>
       <c r="Q57" t="str">
-        <v>백현동558</v>
+        <v>백현동560</v>
       </c>
       <c r="R57" t="str">
         <v/>
       </c>
       <c r="S57" t="str">
-        <v>백현마을8단지 아파트 입구</v>
+        <v>블레도르 앞 도로(판교역로2번길40)</v>
       </c>
       <c r="T57" t="str">
         <v/>
@@ -3778,13 +3778,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>26-12</v>
+        <v>26-13</v>
       </c>
       <c r="B58" t="str">
         <v>판교역로</v>
       </c>
       <c r="C58" t="str">
-        <v>26-성남시-12</v>
+        <v>26-성남시-13</v>
       </c>
       <c r="D58" t="str">
         <v>양호</v>
@@ -3826,13 +3826,13 @@
         <v>-</v>
       </c>
       <c r="Q58" t="str">
-        <v>백현동560</v>
+        <v>백현동564-5</v>
       </c>
       <c r="R58" t="str">
         <v/>
       </c>
       <c r="S58" t="str">
-        <v>블레도르 앞 도로(판교역로2번길40)</v>
+        <v>세븐일레븐 앞 도로(판교역로14번길 20)</v>
       </c>
       <c r="T58" t="str">
         <v/>
@@ -3840,13 +3840,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>26-13</v>
+        <v>26-14</v>
       </c>
       <c r="B59" t="str">
         <v>판교역로</v>
       </c>
       <c r="C59" t="str">
-        <v>26-성남시-13</v>
+        <v>26-성남시-14</v>
       </c>
       <c r="D59" t="str">
         <v>양호</v>
@@ -3888,13 +3888,13 @@
         <v>-</v>
       </c>
       <c r="Q59" t="str">
-        <v>백현동564-5</v>
+        <v>백현동578-10</v>
       </c>
       <c r="R59" t="str">
         <v/>
       </c>
       <c r="S59" t="str">
-        <v>세븐일레븐 앞 도로(판교역로14번길 20)</v>
+        <v>앞 도로(판교역로12)</v>
       </c>
       <c r="T59" t="str">
         <v/>
@@ -3902,13 +3902,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>26-14</v>
+        <v>26-15</v>
       </c>
       <c r="B60" t="str">
-        <v>판교역로</v>
+        <v>성남대로</v>
       </c>
       <c r="C60" t="str">
-        <v>26-성남시-14</v>
+        <v>26-성남시-15</v>
       </c>
       <c r="D60" t="str">
         <v>양호</v>
@@ -3950,13 +3950,13 @@
         <v>-</v>
       </c>
       <c r="Q60" t="str">
-        <v>백현동578-10</v>
+        <v>정자동7</v>
       </c>
       <c r="R60" t="str">
         <v/>
       </c>
       <c r="S60" t="str">
-        <v>앞 도로(판교역로12)</v>
+        <v>두산위브파빌리온 앞 도로(성남대로393)</v>
       </c>
       <c r="T60" t="str">
         <v/>
@@ -3964,13 +3964,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>26-15</v>
+        <v>26-16</v>
       </c>
       <c r="B61" t="str">
         <v>성남대로</v>
       </c>
       <c r="C61" t="str">
-        <v>26-성남시-15</v>
+        <v>26-성남시-16</v>
       </c>
       <c r="D61" t="str">
         <v>양호</v>
@@ -4012,13 +4012,13 @@
         <v>-</v>
       </c>
       <c r="Q61" t="str">
-        <v>정자동7</v>
+        <v>정자동15-1</v>
       </c>
       <c r="R61" t="str">
         <v/>
       </c>
       <c r="S61" t="str">
-        <v>두산위브파빌리온 앞 도로(성남대로393)</v>
+        <v>할머니부뚜막_정자점(성남대로389)</v>
       </c>
       <c r="T61" t="str">
         <v/>
@@ -4026,13 +4026,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>26-16</v>
+        <v>26-17</v>
       </c>
       <c r="B62" t="str">
         <v>성남대로</v>
       </c>
       <c r="C62" t="str">
-        <v>26-성남시-16</v>
+        <v>26-성남시-17</v>
       </c>
       <c r="D62" t="str">
         <v>양호</v>
@@ -4074,13 +4074,13 @@
         <v>-</v>
       </c>
       <c r="Q62" t="str">
-        <v>정자동15-1</v>
+        <v>정자동15-3</v>
       </c>
       <c r="R62" t="str">
         <v/>
       </c>
       <c r="S62" t="str">
-        <v>할머니부뚜막_정자점(성남대로389)</v>
+        <v>폴라리스빌딩 앞 도로(성남대로381)</v>
       </c>
       <c r="T62" t="str">
         <v/>
@@ -4088,13 +4088,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>26-17</v>
+        <v>26-18</v>
       </c>
       <c r="B63" t="str">
         <v>성남대로</v>
       </c>
       <c r="C63" t="str">
-        <v>26-성남시-17</v>
+        <v>26-성남시-18</v>
       </c>
       <c r="D63" t="str">
         <v>양호</v>
@@ -4136,13 +4136,13 @@
         <v>-</v>
       </c>
       <c r="Q63" t="str">
-        <v>정자동15-3</v>
+        <v>정자동15-4</v>
       </c>
       <c r="R63" t="str">
         <v/>
       </c>
       <c r="S63" t="str">
-        <v>폴라리스빌딩 앞 도로(성남대로381)</v>
+        <v>위브제니스아파트 앞 도로(정자일로232번길25)</v>
       </c>
       <c r="T63" t="str">
         <v/>
@@ -4150,19 +4150,19 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>26-18</v>
+        <v>26-19</v>
       </c>
       <c r="B64" t="str">
         <v>성남대로</v>
       </c>
       <c r="C64" t="str">
-        <v>26-성남시-18</v>
+        <v>26-성남시-19</v>
       </c>
       <c r="D64" t="str">
         <v>양호</v>
       </c>
       <c r="E64" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F64" t="str">
         <v>양호</v>
@@ -4177,7 +4177,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K64" t="str">
         <v>0</v>
@@ -4189,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="N64" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O64" t="str">
         <v>일반</v>
@@ -4198,13 +4198,13 @@
         <v>-</v>
       </c>
       <c r="Q64" t="str">
-        <v>정자동15-4</v>
+        <v>정자동17-2</v>
       </c>
       <c r="R64" t="str">
         <v/>
       </c>
       <c r="S64" t="str">
-        <v>위브제니스아파트 앞 도로(정자일로232번길25)</v>
+        <v>정자역 #5번출구 앞 도로(느티로22)</v>
       </c>
       <c r="T64" t="str">
         <v/>
@@ -4212,19 +4212,19 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>26-19</v>
+        <v>26-20</v>
       </c>
       <c r="B65" t="str">
         <v>성남대로</v>
       </c>
       <c r="C65" t="str">
-        <v>26-성남시-19</v>
+        <v>26-성남시-20</v>
       </c>
       <c r="D65" t="str">
         <v>양호</v>
       </c>
       <c r="E65" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F65" t="str">
         <v>양호</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K65" t="str">
         <v>0</v>
@@ -4251,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="N65" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O65" t="str">
         <v>일반</v>
@@ -4260,13 +4260,13 @@
         <v>-</v>
       </c>
       <c r="Q65" t="str">
-        <v>정자동17-2</v>
+        <v>정자동17-6</v>
       </c>
       <c r="R65" t="str">
         <v/>
       </c>
       <c r="S65" t="str">
-        <v>정자역 #5번출구 앞 도로(느티로22)</v>
+        <v>기아_분당지점 앞 도로(성남대로345)</v>
       </c>
       <c r="T65" t="str">
         <v/>
@@ -4274,19 +4274,19 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>26-20</v>
+        <v>26-21</v>
       </c>
       <c r="B66" t="str">
         <v>성남대로</v>
       </c>
       <c r="C66" t="str">
-        <v>26-성남시-20</v>
+        <v>26-성남시-21</v>
       </c>
       <c r="D66" t="str">
         <v>양호</v>
       </c>
       <c r="E66" t="str">
-        <v>거북등</v>
+        <v>양호</v>
       </c>
       <c r="F66" t="str">
         <v>양호</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="J66" t="str">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K66" t="str">
         <v>0</v>
@@ -4313,22 +4313,22 @@
         <v>0</v>
       </c>
       <c r="N66" t="str">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O66" t="str">
         <v>일반</v>
       </c>
       <c r="P66" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q66" t="str">
-        <v>정자동17-6</v>
+        <v>정자동99-5</v>
       </c>
       <c r="R66" t="str">
         <v/>
       </c>
       <c r="S66" t="str">
-        <v>기아_분당지점 앞 도로(성남대로345)</v>
+        <v>정자역 프라자빌딩 맞음편 버스정류장 앞 도로(성남대로345)</v>
       </c>
       <c r="T66" t="str">
         <v/>
@@ -4336,19 +4336,19 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>26-21</v>
+        <v>26-22</v>
       </c>
       <c r="B67" t="str">
         <v>성남대로</v>
       </c>
       <c r="C67" t="str">
-        <v>26-성남시-21</v>
+        <v>26-성남시-22</v>
       </c>
       <c r="D67" t="str">
         <v>양호</v>
       </c>
       <c r="E67" t="str">
-        <v>양호</v>
+        <v>거북등</v>
       </c>
       <c r="F67" t="str">
         <v>양호</v>
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K67" t="str">
         <v>0</v>
@@ -4375,22 +4375,22 @@
         <v>0</v>
       </c>
       <c r="N67" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O67" t="str">
         <v>일반</v>
       </c>
       <c r="P67" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q67" t="str">
-        <v>정자동99-5</v>
+        <v>정자동26-1</v>
       </c>
       <c r="R67" t="str">
         <v/>
       </c>
       <c r="S67" t="str">
-        <v>정자역 프라자빌딩 맞음편 버스정류장 앞 도로(성남대로345)</v>
+        <v>정자역 #3번출구 앞 양차선</v>
       </c>
       <c r="T67" t="str">
         <v/>
@@ -4398,13 +4398,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>26-22</v>
+        <v>26-23</v>
       </c>
       <c r="B68" t="str">
         <v>성남대로</v>
       </c>
       <c r="C68" t="str">
-        <v>26-성남시-22</v>
+        <v>26-성남시-23</v>
       </c>
       <c r="D68" t="str">
         <v>양호</v>
@@ -4446,13 +4446,13 @@
         <v>-</v>
       </c>
       <c r="Q68" t="str">
-        <v>정자동26-1</v>
+        <v>정자동156-2</v>
       </c>
       <c r="R68" t="str">
         <v/>
       </c>
       <c r="S68" t="str">
-        <v>정자역 #3번출구 앞 양차선</v>
+        <v>백궁프라자3 앞 양차선(성남대로331번길3-9)</v>
       </c>
       <c r="T68" t="str">
         <v/>
@@ -4460,19 +4460,19 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>26-23</v>
+        <v>26-24</v>
       </c>
       <c r="B69" t="str">
         <v>성남대로</v>
       </c>
       <c r="C69" t="str">
-        <v>26-성남시-23</v>
+        <v>26-성남시-24</v>
       </c>
       <c r="D69" t="str">
         <v>양호</v>
       </c>
       <c r="E69" t="str">
-        <v>거북등</v>
+        <v>종,횡균열</v>
       </c>
       <c r="F69" t="str">
         <v>양호</v>
@@ -4487,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K69" t="str">
         <v>0</v>
@@ -4499,7 +4499,7 @@
         <v>0</v>
       </c>
       <c r="N69" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O69" t="str">
         <v>일반</v>
@@ -4508,13 +4508,13 @@
         <v>-</v>
       </c>
       <c r="Q69" t="str">
-        <v>정자동156-2</v>
+        <v>정자동156-3</v>
       </c>
       <c r="R69" t="str">
         <v/>
       </c>
       <c r="S69" t="str">
-        <v>백궁프라자3 앞 양차선(성남대로331번길3-9)</v>
+        <v>대명제스트빌딩 앞 양차선(성남대로331번길 3-13)</v>
       </c>
       <c r="T69" t="str">
         <v/>
@@ -4522,19 +4522,19 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>26-24</v>
+        <v>26-25</v>
       </c>
       <c r="B70" t="str">
         <v>성남대로</v>
       </c>
       <c r="C70" t="str">
-        <v>26-성남시-24</v>
+        <v>26-성남시-25</v>
       </c>
       <c r="D70" t="str">
         <v>양호</v>
       </c>
       <c r="E70" t="str">
-        <v>종,횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F70" t="str">
         <v>양호</v>
@@ -4549,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K70" t="str">
         <v>0</v>
@@ -4561,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="N70" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O70" t="str">
         <v>일반</v>
@@ -4570,13 +4570,13 @@
         <v>-</v>
       </c>
       <c r="Q70" t="str">
-        <v>정자동156-3</v>
+        <v>금곡교사거리</v>
       </c>
       <c r="R70" t="str">
         <v/>
       </c>
       <c r="S70" t="str">
-        <v>대명제스트빌딩 앞 양차선(성남대로331번길 3-13)</v>
+        <v>금곡교 사거리</v>
       </c>
       <c r="T70" t="str">
         <v/>
@@ -4584,13 +4584,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>26-25</v>
+        <v>26-26</v>
       </c>
       <c r="B71" t="str">
         <v>성남대로</v>
       </c>
       <c r="C71" t="str">
-        <v>26-성남시-25</v>
+        <v>26-성남시-26</v>
       </c>
       <c r="D71" t="str">
         <v>양호</v>
@@ -4632,21 +4632,269 @@
         <v>-</v>
       </c>
       <c r="Q71" t="str">
-        <v>금곡교사거리</v>
+        <v>정자동168-1</v>
       </c>
       <c r="R71" t="str">
         <v/>
       </c>
       <c r="S71" t="str">
-        <v>금곡교 사거리</v>
+        <v>대림아크리텔 A동 앞 도로(성남대로295)</v>
       </c>
       <c r="T71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>26-27</v>
+      </c>
+      <c r="B72" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C72" t="str">
+        <v>26-성남시-27</v>
+      </c>
+      <c r="D72" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E72" t="str">
+        <v>횡균열</v>
+      </c>
+      <c r="F72" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G72" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H72" t="str">
+        <v>-</v>
+      </c>
+      <c r="I72" t="str">
+        <v>0</v>
+      </c>
+      <c r="J72" t="str">
+        <v>1</v>
+      </c>
+      <c r="K72" t="str">
+        <v>0</v>
+      </c>
+      <c r="L72" t="str">
+        <v>1</v>
+      </c>
+      <c r="M72" t="str">
+        <v>0</v>
+      </c>
+      <c r="N72" t="str">
+        <v>2</v>
+      </c>
+      <c r="O72" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P72" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q72" t="str">
+        <v>정자동168-4</v>
+      </c>
+      <c r="R72" t="str">
+        <v/>
+      </c>
+      <c r="S72" t="str">
+        <v>대림아크릴텔C동 앞 도로(성남대로295)</v>
+      </c>
+      <c r="T72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>26-28</v>
+      </c>
+      <c r="B73" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C73" t="str">
+        <v>26-성남시-28</v>
+      </c>
+      <c r="D73" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E73" t="str">
+        <v>종,횡균열</v>
+      </c>
+      <c r="F73" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G73" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H73" t="str">
+        <v>-</v>
+      </c>
+      <c r="I73" t="str">
+        <v>0</v>
+      </c>
+      <c r="J73" t="str">
+        <v>1</v>
+      </c>
+      <c r="K73" t="str">
+        <v>0</v>
+      </c>
+      <c r="L73" t="str">
+        <v>1</v>
+      </c>
+      <c r="M73" t="str">
+        <v>0</v>
+      </c>
+      <c r="N73" t="str">
+        <v>2</v>
+      </c>
+      <c r="O73" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P73" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q73" t="str">
+        <v>정자동99-7</v>
+      </c>
+      <c r="R73" t="str">
+        <v/>
+      </c>
+      <c r="S73" t="str">
+        <v>아데나팰리스 C동 맟춤정장마테아 맞음편 도로(성남대로275)</v>
+      </c>
+      <c r="T73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>26-29</v>
+      </c>
+      <c r="B74" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C74" t="str">
+        <v>26-성남시-29</v>
+      </c>
+      <c r="D74" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E74" t="str">
+        <v>종균열</v>
+      </c>
+      <c r="F74" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G74" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H74" t="str">
+        <v>-</v>
+      </c>
+      <c r="I74" t="str">
+        <v>0</v>
+      </c>
+      <c r="J74" t="str">
+        <v>1</v>
+      </c>
+      <c r="K74" t="str">
+        <v>0</v>
+      </c>
+      <c r="L74" t="str">
+        <v>1</v>
+      </c>
+      <c r="M74" t="str">
+        <v>0</v>
+      </c>
+      <c r="N74" t="str">
+        <v>2</v>
+      </c>
+      <c r="O74" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P74" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q74" t="str">
+        <v>정자동169-1</v>
+      </c>
+      <c r="R74" t="str">
+        <v/>
+      </c>
+      <c r="S74" t="str">
+        <v>아데나펠리스 아데나공인중개사 앞 도로(성남대로275)</v>
+      </c>
+      <c r="T74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>26-30</v>
+      </c>
+      <c r="B75" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C75" t="str">
+        <v>26-성남시-30</v>
+      </c>
+      <c r="D75" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E75" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F75" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G75" t="str">
+        <v>14.5</v>
+      </c>
+      <c r="H75" t="str">
+        <v>-</v>
+      </c>
+      <c r="I75" t="str">
+        <v>0</v>
+      </c>
+      <c r="J75" t="str">
+        <v>3</v>
+      </c>
+      <c r="K75" t="str">
+        <v>0</v>
+      </c>
+      <c r="L75" t="str">
+        <v>1</v>
+      </c>
+      <c r="M75" t="str">
+        <v>0</v>
+      </c>
+      <c r="N75" t="str">
+        <v>4</v>
+      </c>
+      <c r="O75" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P75" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q75" t="str">
+        <v>불정교사거리</v>
+      </c>
+      <c r="R75" t="str">
+        <v/>
+      </c>
+      <c r="S75" t="str">
+        <v>불정교사거리</v>
+      </c>
+      <c r="T75" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T75"/>
   </ignoredErrors>
 </worksheet>
 </file>